--- a/docs/00_构建与版本/版本改动与测试/CUBE版本改动记录_售后版.xlsx
+++ b/docs/00_构建与版本/版本改动与测试/CUBE版本改动记录_售后版.xlsx
@@ -215,18 +215,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReleaseChanges" displayName="ReleaseChanges" ref="A5:F121" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:F121"/>
-  <x:tableColumns count="6">
-    <x:tableColumn id="1" name="发布日期"/>
-    <x:tableColumn id="2" name="CPU2 版本"/>
-    <x:tableColumn id="3" name="CPU3 版本"/>
-    <x:tableColumn id="4" name="主要改动"/>
-    <x:tableColumn id="5" name="改动点或修复的问题"/>
-    <x:tableColumn id="6" name="售后注意事项"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReleaseChanges" displayName="ReleaseChanges" ref="A5:F122" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:F122"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="发布日期"/>
+    <tableColumn id="2" name="CPU2 版本"/>
+    <tableColumn id="3" name="CPU3 版本"/>
+    <tableColumn id="4" name="主要改动"/>
+    <tableColumn id="5" name="改动点或修复的问题"/>
+    <tableColumn id="6" name="售后注意事项"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -516,22 +516,62 @@
         <v>售后注意事项</v>
       </c>
     </row>
-    <row r="6" ht="89" customHeight="1">
+    <row r="6" ht="154" customHeight="1">
       <c r="A6" s="25" t="n">
         <v>46272</v>
       </c>
-      <c r="B6" s="27" t="str">
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V1.44.0.0</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V1.43.0.0</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">称重探底与
+下行保护</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 探底扭力阈值改为开始检测后需要减少的重量，名称不变。
+2. 接近预计罐底才检测并分段减速，减少低速运行距离。
+3. 触底后补偿刹车过行程上提，收到新称重且恢复后再精找。
+4. 两次精找位置相差不超过 10 mm 才确认罐底。
+5. 下行增加固定 500 的绝对低重量保护，保留相对变轻保护。
+6. 通信、释放和运动故障不再被参考罐高回退掩盖。
+7. SI 分布首点必须高于探底释放位置，不再自动改写首点。</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 两块板配套升级至协议 37。
+2. 原阈值数值保留，升级前记录并按减重量重新复核；固定下限 500 为原始计数。
+3. 称重探底阈值不能为 0。
+4. 需验证噪声、制动距离和 SI 首点配置；尚未完成目标板测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="89" customHeight="1">
+      <c r="A7" s="25" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B7" s="27" t="str">
         <v>V1.43.0.0</v>
       </c>
-      <c r="C6" s="27" t="str">
+      <c r="C7" s="27" t="str">
         <v>V1.42.0.0</v>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>液位定时矫正</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">1. 新增“定时矫正”和“矫正周期”设置。
 2. 设备稳定跟随液位后，可按周期重新检查找液位所用的参考频率。
@@ -540,2717 +580,2717 @@
 5. 矫正失败会尝试恢复，多次失败后报故障。</t>
         </is>
       </c>
-      <c r="F6" s="23" t="str">
+      <c r="F7" s="23" t="str">
         <v>两块板需配套升级。默认关闭，间隔默认 1440
 分钟（1 天），可设 60～10080 分钟；连续失败
 可能报 15-34。</v>
       </c>
     </row>
-    <row r="7" ht="74" customHeight="1">
-      <c r="A7" s="26" t="n">
+    <row r="8" ht="74" customHeight="1">
+      <c r="A8" s="26" t="n">
         <v>46270</v>
       </c>
-      <c r="B7" s="28" t="str">
+      <c r="B8" s="28" t="str">
         <v>V1.42.11.0</v>
       </c>
-      <c r="C7" s="28" t="str">
+      <c r="C8" s="28" t="str">
         <v>V1.41.0.0</v>
       </c>
-      <c r="D7" s="24" t="str">
+      <c r="D8" s="24" t="str">
         <v>修复液位跟随时的
 丢步误报</v>
       </c>
-      <c r="E7" s="24" t="str">
+      <c r="E8" s="24" t="str">
         <v>1. 修复方式 5 换向、变速时，误报电机没有走够距离（丢步）的问题。
 2. 停止等待时不再按仍在运动计算，减少误报。
 3. 探头抖动或回退时，不重复计算前进距离。</v>
       </c>
-      <c r="F7" s="24" t="str">
+      <c r="F8" s="24" t="str">
         <v>本次不包含称重探底的可靠性改造。</v>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="25" t="n">
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="25" t="n">
         <v>46270</v>
       </c>
-      <c r="B8" s="27" t="str">
+      <c r="B9" s="27" t="str">
         <v>V1.42.10.0</v>
       </c>
-      <c r="C8" s="27" t="str">
+      <c r="C9" s="27" t="str">
         <v>V1.41.0.0</v>
       </c>
-      <c r="D8" s="23" t="str">
+      <c r="D9" s="23" t="str">
         <v>新增两路常亮面板
 指示灯</v>
       </c>
-      <c r="E8" s="23" t="str">
+      <c r="E9" s="23" t="str">
         <v>1. 新增两路面板指示灯控制，按现有接线保持常亮。</v>
       </c>
-      <c r="F8" s="23" t="str">
+      <c r="F9" s="23" t="str">
         <v>该版不会根据运行或故障状态改变闪烁方式。</v>
       </c>
     </row>
-    <row r="9" ht="74" customHeight="1">
-      <c r="A9" s="26" t="n">
+    <row r="10" ht="74" customHeight="1">
+      <c r="A10" s="26" t="n">
         <v>46269</v>
       </c>
-      <c r="B9" s="28" t="str">
+      <c r="B10" s="28" t="str">
         <v>V1.42.10.0</v>
       </c>
-      <c r="C9" s="28" t="str">
+      <c r="C10" s="28" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D9" s="24" t="str">
+      <c r="D10" s="24" t="str">
         <v>调整 SI 首点位置和
 读数等待</v>
       </c>
-      <c r="E9" s="24" t="str">
+      <c r="E10" s="24" t="str">
         <v>1. 探底后，上提 100 mm 的停机位置直接作为第 0 测点，不再多向下
    走一次。
 2. 到达每个测点后，先切密度模式，再按设置时间等待。
 3. 读数为零或还不能使用时先继续等待，不立即认定探头已在空气中。</v>
       </c>
-      <c r="F9" s="24" t="str">
+      <c r="F10" s="24" t="str">
         <v>每点最多等待 5 分钟；到时仍按原有规则选用结果
 或报错。</v>
       </c>
     </row>
-    <row r="10" ht="74" customHeight="1">
-      <c r="A10" s="25" t="n">
+    <row r="11" ht="74" customHeight="1">
+      <c r="A11" s="25" t="n">
         <v>46268</v>
       </c>
-      <c r="B10" s="27" t="str">
+      <c r="B11" s="27" t="str">
         <v>V1.42.9.0</v>
       </c>
-      <c r="C10" s="27" t="str">
+      <c r="C11" s="27" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D10" s="23" t="str">
+      <c r="D11" s="23" t="str">
         <v>增加 V4 通信重试和
 液位等待</v>
       </c>
-      <c r="E10" s="23" t="str">
+      <c r="E11" s="23" t="str">
         <v>1. 可安全重复的读取操作通信失败后，最多尝试 3 次。
 2. 液位频率为 0 时，先停机等待读数稳定。
 3. 自动恢复增加次数限制，避免故障后一直重复检查。
 4. 记录失败时收到的数据，方便售后提供给研发排查。</v>
       </c>
-      <c r="F10" s="23" t="str">
+      <c r="F11" s="23" t="str">
         <v>修改参数、取水和磁零点等动作不会盲目重发；读
 数未稳定不当通信故障。</v>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="26" t="n">
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="B11" s="28" t="str">
+      <c r="B12" s="28" t="str">
         <v>V1.42.8.0</v>
       </c>
-      <c r="C11" s="28" t="str">
+      <c r="C12" s="28" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D11" s="24" t="str">
+      <c r="D12" s="24" t="str">
         <v>增加 V4 通信间隔和
 不稳定提示</v>
       </c>
-      <c r="E11" s="24" t="str">
+      <c r="E12" s="24" t="str">
         <v>1. 每次 V4 通信后留出至少 30 毫秒间隔，避免请求过密。
 2. 读到负频率时，提示当前频率不稳定。</v>
       </c>
-      <c r="F11" s="24" t="str">
+      <c r="F12" s="24" t="str">
         <v>本次增加间隔和提示，原有数值处理方法不变。</v>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="25" t="n">
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="25" t="n">
         <v>46260</v>
       </c>
-      <c r="B12" s="27" t="str">
+      <c r="B13" s="27" t="str">
         <v>V1.42.7.0</v>
       </c>
-      <c r="C12" s="27" t="str">
+      <c r="C13" s="27" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D12" s="23" t="str">
+      <c r="D13" s="23" t="str">
         <v>修复 V4 读数未稳时
 的通信误报</v>
       </c>
-      <c r="E12" s="23" t="str">
+      <c r="E13" s="23" t="str">
         <v>1. 修复 V4 读数暂未稳定时，被误报为通信故障的问题。
 2. 主动上传和请求读取两种方式，采用相同的无读数处理。</v>
       </c>
-      <c r="F12" s="23" t="str">
+      <c r="F13" s="23" t="str">
         <v>未稳定的值不能当作本次实测结果；超时、错误
 数据和模式不对仍需排查。</v>
       </c>
     </row>
-    <row r="13" ht="59" customHeight="1">
-      <c r="A13" s="26" t="n">
+    <row r="14" ht="59" customHeight="1">
+      <c r="A14" s="26" t="n">
         <v>46260</v>
       </c>
-      <c r="B13" s="28" t="str">
+      <c r="B14" s="28" t="str">
         <v>V1.42.6.0</v>
       </c>
-      <c r="C13" s="28" t="str">
+      <c r="C14" s="28" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D13" s="24" t="str">
+      <c r="D14" s="24" t="str">
         <v>区分调试版和发布版
 程序包</v>
       </c>
-      <c r="E13" s="24" t="str">
+      <c r="E14" s="24" t="str">
         <v>1. 程序文件区分 DEBUG 调试版和 RELEASE 发布版。
 2. 调试版可接收串口调试命令，发布版不接收这些命令。
 3. 发布版仍保留日志发送、正常测量和业务通信。</v>
       </c>
-      <c r="F13" s="24" t="str">
+      <c r="F14" s="24" t="str">
         <v>需要串口调试时使用 DEBUG 包；RELEASE 不响应
 调试命令不表示串口损坏。</v>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="25" t="n">
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="25" t="n">
         <v>46260</v>
       </c>
-      <c r="B14" s="27" t="str">
+      <c r="B15" s="27" t="str">
         <v>V1.42.5.1</v>
       </c>
-      <c r="C14" s="27" t="str">
+      <c r="C15" s="27" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D14" s="23" t="str">
+      <c r="D15" s="23" t="str">
         <v>调整调试串口未接线
 时的设置</v>
       </c>
-      <c r="E14" s="23" t="str">
+      <c r="E15" s="23" t="str">
         <v>1. 调整调试串口未连接设备时的输入设置。</v>
       </c>
-      <c r="F14" s="23" t="str">
+      <c r="F15" s="23" t="str">
         <v>接线和通信设置不变；原文没有认定本项已修复某
 个具体现场故障。</v>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="26" t="n">
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="26" t="n">
         <v>46260</v>
       </c>
-      <c r="B15" s="28" t="str">
+      <c r="B16" s="28" t="str">
         <v>V1.42.5.0</v>
       </c>
-      <c r="C15" s="28" t="str">
+      <c r="C16" s="28" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D15" s="24" t="str">
+      <c r="D16" s="24" t="str">
         <v>修复 V4 通信测试的
 冲突与误判</v>
       </c>
-      <c r="E15" s="24" t="str">
+      <c r="E16" s="24" t="str">
         <v>1. 修复 SC 测试与 V4 自动上传互相影响的问题。
 2. 探头在空气中暂时测不出密度时，可仍判断通信正常。</v>
       </c>
-      <c r="F15" s="24" t="str">
+      <c r="F16" s="24" t="str">
         <v>通信正常不代表已有测量结果；超时或收到错误
 数据仍按异常处理。</v>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="25" t="n">
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="25" t="n">
         <v>46259</v>
       </c>
-      <c r="B16" s="27" t="str">
+      <c r="B17" s="27" t="str">
         <v>V1.42.4.0</v>
       </c>
-      <c r="C16" s="27" t="str">
+      <c r="C17" s="27" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D16" s="23" t="str">
+      <c r="D17" s="23" t="str">
         <v>读取部件参数前先切
 密度模式</v>
       </c>
-      <c r="E16" s="23" t="str">
+      <c r="E17" s="23" t="str">
         <v>1. 读取部件参数前先切换到密度模式。
 2. 通信自检前也会确认密度模式，减少从液位模式切入时的误报。</v>
       </c>
-      <c r="F16" s="23" t="str">
+      <c r="F17" s="23" t="str">
         <v>切换失败时保留实际故障，不继续读取密度。</v>
       </c>
     </row>
-    <row r="17" ht="59" customHeight="1">
-      <c r="A17" s="26" t="n">
+    <row r="18" ht="59" customHeight="1">
+      <c r="A18" s="26" t="n">
         <v>46258</v>
       </c>
-      <c r="B17" s="28" t="str">
+      <c r="B18" s="28" t="str">
         <v>V1.42.3.0</v>
       </c>
-      <c r="C17" s="28" t="str">
+      <c r="C18" s="28" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D17" s="24" t="str">
+      <c r="D18" s="24" t="str">
         <v>修复运动完成误判，
 密度未出时等待</v>
       </c>
-      <c r="E17" s="24" t="str">
+      <c r="E18" s="24" t="str">
         <v>1. 修复探头仍在连续移动，却被程序误判已完成的问题。
 2. 电机收到启动要求后仍不转，会停止并报错。
 3. DM4 密度模式暂时读到频率 0 时，继续等待测量结果。</v>
       </c>
-      <c r="F17" s="24" t="str">
+      <c r="F18" s="24" t="str">
         <v>暂未测出密度，不直接等同于通信故障。</v>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="25" t="n">
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="25" t="n">
         <v>46255</v>
       </c>
-      <c r="B18" s="27" t="str">
+      <c r="B19" s="27" t="str">
         <v>V1.42.2.0</v>
       </c>
-      <c r="C18" s="27" t="str">
+      <c r="C19" s="27" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D18" s="23" t="str">
+      <c r="D19" s="23" t="str">
         <v>防止把旧温度、黏度
 当作新读数</v>
       </c>
-      <c r="E18" s="23" t="str">
+      <c r="E19" s="23" t="str">
         <v>1. 温度还未更新时，不把旧温度当作新结果。
 2. 黏度还未更新时，不把旧黏度当作新结果。</v>
       </c>
-      <c r="F18" s="23" t="str">
+      <c r="F19" s="23" t="str">
         <v>只调整何时采用读数，通信方式和参数地址不变。</v>
       </c>
     </row>
-    <row r="19" ht="74" customHeight="1">
-      <c r="A19" s="26" t="n">
+    <row r="20" ht="74" customHeight="1">
+      <c r="A20" s="26" t="n">
         <v>46255</v>
       </c>
-      <c r="B19" s="28" t="str">
+      <c r="B20" s="28" t="str">
         <v>V1.42.1.0</v>
       </c>
-      <c r="C19" s="28" t="str">
+      <c r="C20" s="28" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D19" s="24" t="str">
+      <c r="D20" s="24" t="str">
         <v>切换操作先停机，
 探底失败沿用罐高</v>
       </c>
-      <c r="E19" s="24" t="str">
+      <c r="E20" s="24" t="str">
         <v>1. 切换操作时先停机退出，不再误记为测量故障。
 2. 恢复原有做法：探底失败或偏差过大时，使用已设置的罐高作为后续
    参考。
 3. 统一液位、水位变化后电流数据的更新。</v>
       </c>
-      <c r="F19" s="24" t="str">
+      <c r="F20" s="24" t="str">
         <v>采用设置罐高作为参考，不代表本次已经实测到罐
 底。</v>
       </c>
     </row>
-    <row r="20" ht="59" customHeight="1">
-      <c r="A20" s="25" t="n">
+    <row r="21" ht="59" customHeight="1">
+      <c r="A21" s="25" t="n">
         <v>46253</v>
       </c>
-      <c r="B20" s="27" t="str">
+      <c r="B21" s="27" t="str">
         <v>V1.42.0.0</v>
       </c>
-      <c r="C20" s="27" t="str">
+      <c r="C21" s="27" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D20" s="23" t="str">
+      <c r="D21" s="23" t="str">
         <v>新增 V3/V4 参数修改
 与读取核对</v>
       </c>
-      <c r="E20" s="23" t="str">
+      <c r="E21" s="23" t="str">
         <v>1. 新增通过调试串口修改传感器参数的命令。
 2. 修改后重新读取，确认实际值。
 3. V4 只允许在识别成功、通信方式正确时修改指定范围的参数。</v>
       </c>
-      <c r="F20" s="23" t="str">
+      <c r="F21" s="23" t="str">
         <v>原文漏列协议 34 到 35 的过渡记录，刷机时需
 核对正式配套程序包。</v>
       </c>
     </row>
-    <row r="21" ht="74" customHeight="1">
-      <c r="A21" s="26" t="n">
+    <row r="22" ht="74" customHeight="1">
+      <c r="A22" s="26" t="n">
         <v>46253</v>
       </c>
-      <c r="B21" s="28" t="str">
+      <c r="B22" s="28" t="str">
         <v>V1.41.1.0</v>
       </c>
-      <c r="C21" s="28" t="str">
+      <c r="C22" s="28" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D21" s="24" t="str">
+      <c r="D22" s="24" t="str">
         <v>滑环匹配完成前先
 确认传感器</v>
       </c>
-      <c r="E21" s="24" t="str">
+      <c r="E22" s="24" t="str">
         <v>1. 无线滑环连上后，继续检查传感器类型和编号，全部识别成功才显示
    匹配完成。
 2. 修复识别非 V4 传感器时短暂误报 13-3 的问题。
 3. 无法确认传感器时，测量前会重新识别。</v>
       </c>
-      <c r="F21" s="24" t="str">
+      <c r="F22" s="24" t="str">
         <v>蓝牙已连接，不等于传感器已经可正常测量。</v>
       </c>
     </row>
-    <row r="22" ht="74" customHeight="1">
-      <c r="A22" s="25" t="n">
+    <row r="23" ht="74" customHeight="1">
+      <c r="A23" s="25" t="n">
         <v>46252</v>
       </c>
-      <c r="B22" s="27" t="str">
+      <c r="B23" s="27" t="str">
         <v>V1.41.0.0</v>
       </c>
-      <c r="C22" s="27" t="str">
+      <c r="C23" s="27" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D22" s="23" t="str">
+      <c r="D23" s="23" t="str">
         <v>改善 V4 无线连接并
 增加测试命令</v>
       </c>
-      <c r="E22" s="23" t="str">
+      <c r="E23" s="23" t="str">
         <v>1. 新增 V4 通信、模式和参数测试命令。
 2. 改善 V4 通过无线滑环连接时的识别和数据接收。
 3. 支持编号尚未设置、编号为 0 的 V4 传感器。
 4. 增加丢失数据和错误数据的记录，方便排查。</v>
       </c>
-      <c r="F22" s="23" t="str">
+      <c r="F23" s="23" t="str">
         <v>读数未稳定不直接当通信故障，也不能当实测 0。
 水位和磁零点功能不能同时开启。</v>
       </c>
     </row>
-    <row r="23" ht="59" customHeight="1">
-      <c r="A23" s="26" t="n">
+    <row r="24" ht="59" customHeight="1">
+      <c r="A24" s="26" t="n">
         <v>46251</v>
       </c>
-      <c r="B23" s="28" t="str">
+      <c r="B24" s="28" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="C23" s="28" t="str">
+      <c r="C24" s="28" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="D23" s="24" t="str">
+      <c r="D24" s="24" t="str">
         <v>修复屏幕残影和
 确认键多按一次</v>
       </c>
-      <c r="E23" s="24" t="str">
+      <c r="E24" s="24" t="str">
         <v>1. 修复屏幕异常恢复后可能留下旧画面或残影的问题。
 2. 限制连续恢复次数，避免一直反复重启屏幕。
 3. 修复操作确认页还需额外多按一次确认的问题。</v>
       </c>
-      <c r="F23" s="24" t="str">
+      <c r="F24" s="24" t="str">
         <v>确认页出现后，下一次确认即可执行。</v>
       </c>
     </row>
-    <row r="24" ht="59" customHeight="1">
-      <c r="A24" s="25" t="n">
+    <row r="25" ht="59" customHeight="1">
+      <c r="A25" s="25" t="n">
         <v>46251</v>
       </c>
-      <c r="B24" s="27" t="str">
+      <c r="B25" s="27" t="str">
         <v>V1.40.1.0</v>
       </c>
-      <c r="C24" s="27" t="str">
+      <c r="C25" s="27" t="str">
         <v>V1.40.0.0</v>
       </c>
-      <c r="D24" s="23" t="str">
+      <c r="D25" s="23" t="str">
         <v>液位跟随支持更细的
 低速调整</v>
       </c>
-      <c r="E24" s="23" t="str">
+      <c r="E25" s="23" t="str">
         <v>1. 方式 5 跟随液位时可更慢、更细地调整速度。
 2. 改变方向前先慢停，减少低速阶段误报丢步。
 3. 关闭电流输出后，不再继续操作电流输出硬件。</v>
       </c>
-      <c r="F24" s="23" t="str">
+      <c r="F25" s="23" t="str">
         <v>关闭时屏幕显示的目标电流，不代表实际已输出该
 电流。</v>
       </c>
     </row>
-    <row r="25" ht="59" customHeight="1">
-      <c r="A25" s="26" t="n">
+    <row r="26" ht="59" customHeight="1">
+      <c r="A26" s="26" t="n">
         <v>46248</v>
       </c>
-      <c r="B25" s="28" t="str">
+      <c r="B26" s="28" t="str">
         <v>V1.40.0.0</v>
       </c>
-      <c r="C25" s="28" t="str">
+      <c r="C26" s="28" t="str">
         <v>V1.40.0.0</v>
       </c>
-      <c r="D25" s="24" t="str">
+      <c r="D26" s="24" t="str">
         <v>增加位置异常检查与
 故障提示</v>
       </c>
-      <c r="E25" s="24" t="str">
+      <c r="E26" s="24" t="str">
         <v>1. 增加上电位置变化检查，发现保存位置与当前情况不符时提示故障。
 2. 运行中位置突然跳变时，增加检查和保护。
 3. 完善位置保存和掉电保存，屏幕增加相关故障原因。</v>
       </c>
-      <c r="F25" s="24" t="str">
+      <c r="F26" s="24" t="str">
         <v>两块板需配套。上电位置异常后需按规定回零或标
 零；旧编码轮周长为 0 时按 95.000 mm 处理。</v>
       </c>
     </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="25" t="n">
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="25" t="n">
         <v>46247</v>
       </c>
-      <c r="B26" s="27" t="str">
+      <c r="B27" s="27" t="str">
         <v>V1.39.2.0</v>
       </c>
-      <c r="C26" s="27" t="str">
+      <c r="C27" s="27" t="str">
         <v>V1.39.0.0</v>
       </c>
-      <c r="D26" s="23" t="str">
+      <c r="D27" s="23" t="str">
         <v>新增协议查询，减少
 连接选错</v>
       </c>
-      <c r="E26" s="23" t="str">
+      <c r="E27" s="23" t="str">
         <v>1. 新增查询当前通信协议的功能。
 2. 上位机可据此识别设备，减少自动连接时选错协议。</v>
       </c>
-      <c r="F26" s="23" t="str">
+      <c r="F27" s="23" t="str">
         <v>查询不修改设置；旧程序仍需用旧识别方式。</v>
       </c>
     </row>
-    <row r="27" ht="59" customHeight="1">
-      <c r="A27" s="26" t="n">
+    <row r="28" ht="59" customHeight="1">
+      <c r="A28" s="26" t="n">
         <v>46247</v>
       </c>
-      <c r="B27" s="28" t="str">
+      <c r="B28" s="28" t="str">
         <v>V1.39.2.0</v>
       </c>
-      <c r="C27" s="28" t="str">
+      <c r="C28" s="28" t="str">
         <v>V1.38.2.0</v>
       </c>
-      <c r="D27" s="24" t="str">
+      <c r="D28" s="24" t="str">
         <v>修正固定频率找液位
 的方向和停点</v>
       </c>
-      <c r="E27" s="24" t="str">
+      <c r="E28" s="24" t="str">
         <v>1. 修正方式 5 根据设定频率选择移动方向和速度的处理。
 2. 找到液体后，不再固定多向下走 100 mm。
 3. 到达低液位盲区时停止下行，避免继续向下找。</v>
       </c>
-      <c r="F27" s="24" t="str">
+      <c r="F28" s="24" t="str">
         <v>升级后核对原有频率和阈值设置；LF 测试使用同
 一套方法。</v>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="25" t="n">
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="n">
         <v>46247</v>
       </c>
-      <c r="B28" s="27" t="str">
+      <c r="B29" s="27" t="str">
         <v>V1.39.1.0</v>
       </c>
-      <c r="C28" s="27" t="str">
+      <c r="C29" s="27" t="str">
         <v>V1.38.2.0</v>
       </c>
-      <c r="D28" s="23" t="str">
+      <c r="D29" s="23" t="str">
         <v>减少两块板命令过密
 造成的通信异常</v>
       </c>
-      <c r="E28" s="23" t="str">
+      <c r="E29" s="23" t="str">
         <v>1. 连续查询或操作之间增加必要间隔，减少命令发得过密造成的通信
    异常。</v>
       </c>
-      <c r="F28" s="23" t="str">
+      <c r="F29" s="23" t="str">
         <v>只需升级显示板，原超时和故障恢复处理不变。</v>
       </c>
     </row>
-    <row r="29" ht="59" customHeight="1">
-      <c r="A29" s="26" t="n">
+    <row r="30" ht="59" customHeight="1">
+      <c r="A30" s="26" t="n">
         <v>46245</v>
       </c>
-      <c r="B29" s="28" t="str">
+      <c r="B30" s="28" t="str">
         <v>V1.39.1.0</v>
       </c>
-      <c r="C29" s="28" t="str">
+      <c r="C30" s="28" t="str">
         <v>V1.38.1.0</v>
       </c>
-      <c r="D29" s="24" t="str">
+      <c r="D30" s="24" t="str">
         <v>修正传感器识别并
 统一故障名称</v>
       </c>
-      <c r="E29" s="24" t="str">
+      <c r="E30" s="24" t="str">
         <v>1. 修正 V3、V4、DSM 的识别顺序和编号判断。
 2. 识别完 V4 后，恢复原来的通信方式。
 3. 统一 49 项屏幕、日志和故障表的名称。</v>
       </c>
-      <c r="F29" s="24" t="str">
+      <c r="F30" s="24" t="str">
         <v>该版普通识别不再尝试安全传感器协议；V4 编号为
 0 的支持在后续版本增加。</v>
       </c>
     </row>
-    <row r="30" ht="59" customHeight="1">
-      <c r="A30" s="25" t="n">
+    <row r="31" ht="59" customHeight="1">
+      <c r="A31" s="25" t="n">
         <v>46244</v>
       </c>
-      <c r="B30" s="27" t="str">
+      <c r="B31" s="27" t="str">
         <v>V1.39.0.0</v>
       </c>
-      <c r="C30" s="27" t="str">
+      <c r="C31" s="27" t="str">
         <v>V1.38.0.0</v>
       </c>
-      <c r="D30" s="23" t="str">
+      <c r="D31" s="23" t="str">
         <v>提高电流微调精度，
 补齐 V4 读数</v>
       </c>
-      <c r="E30" s="23" t="str">
+      <c r="E31" s="23" t="str">
         <v>1. 电流修正可以精细到 0.001 mA，屏幕显示三位小数。
 2. V4 读取数据前先检查测量模式，减少模式不对时的错误读数。
 3. 补齐水电容、姿态、黏度等读取。</v>
       </c>
-      <c r="F30" s="23" t="str">
+      <c r="F31" s="23" t="str">
         <v>两块板和 LTD/LH 上位机需配套。旧电流修正值
 自动换算，其他电流设置不能全部照此换算。</v>
       </c>
     </row>
-    <row r="31" ht="59" customHeight="1">
-      <c r="A31" s="26" t="n">
+    <row r="32" ht="59" customHeight="1">
+      <c r="A32" s="26" t="n">
         <v>46242</v>
       </c>
-      <c r="B31" s="28" t="str">
+      <c r="B32" s="28" t="str">
         <v>V1.38.0.0</v>
       </c>
-      <c r="C31" s="28" t="str">
+      <c r="C32" s="28" t="str">
         <v>V1.37.0.0</v>
       </c>
-      <c r="D31" s="24" t="str">
+      <c r="D32" s="24" t="str">
         <v>新增 DSM 版本及更多
 部件信息查询</v>
       </c>
-      <c r="E31" s="24" t="str">
+      <c r="E32" s="24" t="str">
         <v>1. 增加 DSM 传感器版本识别。
 2. 读取部件参数时，增加供电电压、黏度等信息。
 3. 附加信息读不到时，不阻断原有主要参数读取。</v>
       </c>
-      <c r="F31" s="24" t="str">
+      <c r="F32" s="24" t="str">
         <v>不同代际支持的项目不同，少一项附加读数不一定
 是测量故障。</v>
       </c>
     </row>
-    <row r="32" ht="74" customHeight="1">
-      <c r="A32" s="25" t="n">
+    <row r="33" ht="74" customHeight="1">
+      <c r="A33" s="25" t="n">
         <v>46242</v>
       </c>
-      <c r="B32" s="27" t="str">
+      <c r="B33" s="27" t="str">
         <v>V1.37.0.0</v>
       </c>
-      <c r="C32" s="27" t="str">
+      <c r="C33" s="27" t="str">
         <v>V1.37.0.0</v>
       </c>
-      <c r="D32" s="23" t="str">
+      <c r="D33" s="23" t="str">
         <v>新增多参数 V4
 传感器支持</v>
       </c>
-      <c r="E32" s="23" t="str">
+      <c r="E33" s="23" t="str">
         <v>1. 新增多参数 V4 传感器支持，屏幕可显示该类型。
 2. 支持传感器自动上传，也支持设备发出请求后读取。
 3. 可读取密度、频率、温度、水电容、姿态等数据。
 4. 部分纯运动操作在传感器离线时也可执行。</v>
       </c>
-      <c r="F32" s="23" t="str">
+      <c r="F33" s="23" t="str">
         <v>两块板需配套。退回旧程序前，先把传感器参数 65
 改回交互方式，再设置旧程序支持的传感器类型。</v>
       </c>
     </row>
-    <row r="33" ht="59" customHeight="1">
-      <c r="A33" s="26" t="n">
+    <row r="34" ht="59" customHeight="1">
+      <c r="A34" s="26" t="n">
         <v>46241</v>
       </c>
-      <c r="B33" s="28" t="str">
+      <c r="B34" s="28" t="str">
         <v>V1.36.4.0</v>
       </c>
-      <c r="C33" s="28" t="str">
+      <c r="C34" s="28" t="str">
         <v>V1.36.0.0</v>
       </c>
-      <c r="D33" s="24" t="str">
+      <c r="D34" s="24" t="str">
         <v>修复 DSM 通信误报和
 异常倾角显示</v>
       </c>
-      <c r="E33" s="24" t="str">
+      <c r="E34" s="24" t="str">
         <v>1. 修复收到完整传感器回复，却误报数据不完整或通信错误的问题。
 2. 查完蓝牙状态后，确认传感器通信已恢复再继续测量。
 3. 传感器返回的错误提示值，不再显示成真实倾角。</v>
       </c>
-      <c r="F33" s="24" t="str">
+      <c r="F34" s="24" t="str">
         <v>水电容小于 30.0 pF 时仍按原规则处理，不直接
 当作正常读数。</v>
       </c>
     </row>
-    <row r="34" ht="48" customHeight="1">
-      <c r="A34" s="25" t="n">
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="n">
         <v>46241</v>
       </c>
-      <c r="B34" s="27" t="str">
+      <c r="B35" s="27" t="str">
         <v>V1.36.3.0</v>
       </c>
-      <c r="C34" s="27" t="str">
+      <c r="C35" s="27" t="str">
         <v>V1.36.0.0</v>
       </c>
-      <c r="D34" s="23" t="str">
+      <c r="D35" s="23" t="str">
         <v>修复长距离低速移动
 过早报超时</v>
       </c>
-      <c r="E34" s="23" t="str">
+      <c r="E35" s="23" t="str">
         <v>1. 修复低速、长距离移动还没到目标，就在 1 小时被判超时的问题。
 2. 按实际距离和速度安排允许时间，日志可查看已用时间和允许时间。</v>
       </c>
-      <c r="F34" s="23" t="str">
+      <c r="F35" s="23" t="str">
         <v>仍有超时保护，并非一直运行不停止。</v>
       </c>
     </row>
-    <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="26" t="n">
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="26" t="n">
         <v>46238</v>
       </c>
-      <c r="B35" s="28" t="str">
+      <c r="B36" s="28" t="str">
         <v>V1.36.2.0</v>
       </c>
-      <c r="C35" s="28" t="str">
+      <c r="C36" s="28" t="str">
         <v>V1.36.0.0</v>
       </c>
-      <c r="D35" s="24" t="str">
+      <c r="D36" s="24" t="str">
         <v>液位标定后同步调整
 电流量程</v>
       </c>
-      <c r="E35" s="24" t="str">
+      <c r="E36" s="24" t="str">
         <v>1. 液位标定改变罐高后，电流量程会相应调整，不超过新罐高。
 2. 修复旧量程影响电流输出或阻止后续修改参数的问题。</v>
       </c>
-      <c r="F35" s="24" t="str">
+      <c r="F36" s="24" t="str">
         <v>重新标定液位后，核对电流对应的高、低液位。</v>
       </c>
     </row>
-    <row r="36" ht="48" customHeight="1">
-      <c r="A36" s="25" t="n">
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="25" t="n">
         <v>46232</v>
       </c>
-      <c r="B36" s="27" t="str">
+      <c r="B37" s="27" t="str">
         <v>V1.36.1.0</v>
       </c>
-      <c r="C36" s="27" t="str">
+      <c r="C37" s="27" t="str">
         <v>V1.36.0.0</v>
       </c>
-      <c r="D36" s="23" t="str">
+      <c r="D37" s="23" t="str">
         <v>修复蓝牙查询干扰
 传感器通信</v>
       </c>
-      <c r="E36" s="23" t="str">
+      <c r="E37" s="23" t="str">
         <v>1. 修复查完蓝牙信号后，残留回复干扰传感器通信的问题。
 2. 查询中途被新操作打断时，也会恢复传感器通信。</v>
       </c>
-      <c r="F36" s="23" t="str">
+      <c r="F37" s="23" t="str">
         <v>涉及蓝牙信号强度和连接状态查询。</v>
       </c>
     </row>
-    <row r="37" ht="74" customHeight="1">
-      <c r="A37" s="26" t="n">
+    <row r="38" ht="74" customHeight="1">
+      <c r="A38" s="26" t="n">
         <v>46232</v>
       </c>
-      <c r="B37" s="28" t="str">
+      <c r="B38" s="28" t="str">
         <v>V1.36.0.0</v>
       </c>
-      <c r="C37" s="28" t="str">
+      <c r="C38" s="28" t="str">
         <v>V1.36.0.0</v>
       </c>
-      <c r="D37" s="24" t="str">
+      <c r="D38" s="24" t="str">
         <v>新增扭力温度显示，
 修正标定保存</v>
       </c>
-      <c r="E37" s="24" t="str">
+      <c r="E38" s="24" t="str">
         <v>1. 读取部件参数、获取空载或满载扭力时，可查看扭力模块温度。
 2. 收到错误的扭力数据时，不再当作通信恢复正常。
 3. 取消水位标定后立即退出，不继续保存旧结果。
 4. 罐高标定完成规定动作后，才保存新罐高。</v>
       </c>
-      <c r="F37" s="24" t="str">
+      <c r="F38" s="24" t="str">
         <v>两块板需配套。温度显示 --.-- 表示没有可用读数，
 不是 0 ℃。</v>
       </c>
     </row>
-    <row r="38" ht="74" customHeight="1">
-      <c r="A38" s="25" t="n">
+    <row r="39" ht="74" customHeight="1">
+      <c r="A39" s="25" t="n">
         <v>46231</v>
       </c>
-      <c r="B38" s="27" t="str">
+      <c r="B39" s="27" t="str">
         <v>V1.35.0.0</v>
       </c>
-      <c r="C38" s="27" t="str">
+      <c r="C39" s="27" t="str">
         <v>V1.35.0.0</v>
       </c>
-      <c r="D38" s="23" t="str">
+      <c r="D39" s="23" t="str">
         <v>增加低电压停机和
 位置保护</v>
       </c>
-      <c r="E38" s="23" t="str">
+      <c r="E39" s="23" t="str">
         <v>1. 增加 24 V 供电检查，电压过低时禁止运动并尝试保存位置。
 2. 供电检测异常后，设备会有限次数地尝试恢复。
 3. 完善编码器位置保存，位置无法确认时限制相关运动。
 4. 增加供电故障的屏幕提示。</v>
       </c>
-      <c r="F38" s="23" t="str">
+      <c r="F39" s="23" t="str">
         <v>两块板需配套。短暂恢复通信或取消操作，不会
 自动清掉已保持的编码器故障。</v>
       </c>
     </row>
-    <row r="39" ht="74" customHeight="1">
-      <c r="A39" s="26" t="n">
+    <row r="40" ht="74" customHeight="1">
+      <c r="A40" s="26" t="n">
         <v>46228</v>
       </c>
-      <c r="B39" s="28" t="str">
+      <c r="B40" s="28" t="str">
         <v>V1.34.0.0</v>
       </c>
-      <c r="C39" s="28" t="str">
+      <c r="C40" s="28" t="str">
         <v>V1.34.0.0</v>
       </c>
-      <c r="D39" s="24" t="str">
+      <c r="D40" s="24" t="str">
         <v>调整故障编号并提高
 密度允许上限</v>
       </c>
-      <c r="E39" s="24" t="str">
+      <c r="E40" s="24" t="str">
         <v>1. 调整扭力、电流输出等故障的编号和分类。
 2. 密度允许上限从 2000.0 调整为 3000.0 kg/m3。
 3. 通过上位机切换协议时，保留当前串口设置。
 4. 减少上电显示等待，改善外部通信启动。</v>
       </c>
-      <c r="F39" s="24" t="str">
+      <c r="F40" s="24" t="str">
         <v>两块板需配套并使用对应故障表；在屏幕上选协议，
 仍会带出默认串口设置。</v>
       </c>
     </row>
-    <row r="40" ht="89" customHeight="1">
-      <c r="A40" s="25" t="n">
+    <row r="41" ht="89" customHeight="1">
+      <c r="A41" s="25" t="n">
         <v>46228</v>
       </c>
-      <c r="B40" s="27" t="str">
+      <c r="B41" s="27" t="str">
         <v>V1.33.0.0</v>
       </c>
-      <c r="C40" s="27" t="str">
+      <c r="C41" s="27" t="str">
         <v>V1.33.0.0</v>
       </c>
-      <c r="D40" s="23" t="str">
+      <c r="D41" s="23" t="str">
         <v>防止测量目标被改，
 检查报警设置</v>
       </c>
-      <c r="E40" s="23" t="str">
+      <c r="E41" s="23" t="str">
         <v>1. 测量开始后固定使用本次输入的目标，后续修改不会改变正在测量的
    目标。
 2. 自动恢复重测也使用本次目标。
 3. 继电器启用前检查报警值，不允许不合理的上下限设置。
 4. 参数更新期间，其他可用的状态数据可以继续读取。</v>
       </c>
-      <c r="F40" s="23" t="str">
+      <c r="F41" s="23" t="str">
         <v>两块板需配套。设置继电器时可先关闭通道，设好
 各值后再打开；避免屏幕和上位机同时修改。</v>
       </c>
     </row>
-    <row r="41" ht="74" customHeight="1">
-      <c r="A41" s="26" t="n">
+    <row r="42" ht="74" customHeight="1">
+      <c r="A42" s="26" t="n">
         <v>46226</v>
       </c>
-      <c r="B41" s="28" t="str">
+      <c r="B42" s="28" t="str">
         <v>V1.32.0.0</v>
       </c>
-      <c r="C41" s="28" t="str">
+      <c r="C42" s="28" t="str">
         <v>V1.32.0.0</v>
       </c>
-      <c r="D41" s="24" t="str">
+      <c r="D42" s="24" t="str">
         <v>新增液位测试，修复
 区间测量结果</v>
       </c>
-      <c r="E41" s="24" t="str">
+      <c r="E42" s="24" t="str">
         <v>1. 新增 LF 命令，可测试按固定频率寻找液位。
 2. 修复区间测点数量计算错误的问题。
 3. 区间测量失败后，不再显示空结果或不完整结果为测量完成。
 4. 传感器内部出错时，明确返回故障。</v>
       </c>
-      <c r="F41" s="24" t="str">
+      <c r="F42" s="24" t="str">
         <v>LH 新增线圈查询仅用于连接兼容，返回全 0 不
 代表实际设备状态。</v>
       </c>
     </row>
-    <row r="42" ht="59" customHeight="1">
-      <c r="A42" s="25" t="n">
+    <row r="43" ht="59" customHeight="1">
+      <c r="A43" s="25" t="n">
         <v>46226</v>
       </c>
-      <c r="B42" s="27" t="str">
+      <c r="B43" s="27" t="str">
         <v>V1.31.1.0</v>
       </c>
-      <c r="C42" s="27" t="str">
+      <c r="C43" s="27" t="str">
         <v>V1.31.1.0</v>
       </c>
-      <c r="D42" s="23" t="str">
+      <c r="D43" s="23" t="str">
         <v>测量期间限制修改
 设备设置</v>
       </c>
-      <c r="E42" s="23" t="str">
+      <c r="E43" s="23" t="str">
         <v>1. 测量或自动恢复期间，不允许修改普通设备设置。
 2. 设备停在故障状态且没有继续执行任务时，可以修正参数。
 3. 调整程序运行监测，缩短检查间隔。</v>
       </c>
-      <c r="F42" s="23" t="str">
+      <c r="F43" s="23" t="str">
         <v>提示设备忙时，先停止测量并确认待机，再修改
 设置。</v>
       </c>
     </row>
-    <row r="43" ht="74" customHeight="1">
-      <c r="A43" s="26" t="n">
+    <row r="44" ht="74" customHeight="1">
+      <c r="A44" s="26" t="n">
         <v>46226</v>
       </c>
-      <c r="B43" s="28" t="str">
+      <c r="B44" s="28" t="str">
         <v>V1.31.0.0</v>
       </c>
-      <c r="C43" s="28" t="str">
+      <c r="C44" s="28" t="str">
         <v>V1.31.0.0</v>
       </c>
-      <c r="D43" s="24" t="str">
+      <c r="D44" s="24" t="str">
         <v>新增屏幕维护操作和
 报警清除</v>
       </c>
-      <c r="E43" s="24" t="str">
+      <c r="E44" s="24" t="str">
         <v>1. 屏幕可进入、退出维护模式。
 2. 屏幕可清除全部继电器保持的报警。
 3. 新增维护和模拟电流测试的状态提示。
 4. 继电器页可查看是否禁止动作，以及程序要求的最终动作。</v>
       </c>
-      <c r="F43" s="24" t="str">
+      <c r="F44" s="24" t="str">
         <v>“指令已发送”不等于设备已执行完成；继电器
 实际接点还需现场检查。</v>
       </c>
     </row>
-    <row r="44" ht="74" customHeight="1">
-      <c r="A44" s="25" t="n">
+    <row r="45" ht="74" customHeight="1">
+      <c r="A45" s="25" t="n">
         <v>46225</v>
       </c>
-      <c r="B44" s="27" t="str">
+      <c r="B45" s="27" t="str">
         <v>V1.31.0.0</v>
       </c>
-      <c r="C44" s="27" t="str">
+      <c r="C45" s="27" t="str">
         <v>V1.30.0.0</v>
       </c>
-      <c r="D44" s="23" t="str">
+      <c r="D45" s="23" t="str">
         <v>新增 LH 通信及电流、
 报警维护操作</v>
       </c>
-      <c r="E44" s="23" t="str">
+      <c r="E45" s="23" t="str">
         <v>1. 新增 LH 通信功能。
 2. 新增电流修正、退出维护和清除全部继电器保持报警的操作。
 3. SI 的停止命令改为直接停止测量。
 4. 调整通信地址，LTD 默认通信改为 4800 8N1。</v>
       </c>
-      <c r="F44" s="23" t="str">
+      <c r="F45" s="23" t="str">
         <v>两块板及直接使用旧 LTD 地址的上位机需一起适配。
 升级后核对电流和通信设置。</v>
       </c>
     </row>
-    <row r="45" ht="59" customHeight="1">
-      <c r="A45" s="26" t="n">
+    <row r="46" ht="59" customHeight="1">
+      <c r="A46" s="26" t="n">
         <v>46224</v>
       </c>
-      <c r="B45" s="28" t="str">
+      <c r="B46" s="28" t="str">
         <v>V1.30.1.0</v>
       </c>
-      <c r="C45" s="28" t="str">
+      <c r="C46" s="28" t="str">
         <v>V1.29.1.0</v>
       </c>
-      <c r="D45" s="24" t="str">
+      <c r="D46" s="24" t="str">
         <v>修复通信数据异常
 导致设备卡住</v>
       </c>
-      <c r="E45" s="24" t="str">
+      <c r="E46" s="24" t="str">
         <v>1. 修复连续收到大量数据或错误数据后，设备可能卡住不响应的问题。
 2. 通信异常的端口会单独尝试恢复。
 3. 收到过长或不完整的数据时，丢弃后重新接收。</v>
       </c>
-      <c r="F45" s="24" t="str">
+      <c r="F46" s="24" t="str">
         <v>正常通信格式和现场参数不变。</v>
       </c>
     </row>
-    <row r="46" ht="74" customHeight="1">
-      <c r="A46" s="25" t="n">
+    <row r="47" ht="74" customHeight="1">
+      <c r="A47" s="25" t="n">
         <v>46223</v>
       </c>
-      <c r="B46" s="27" t="str">
+      <c r="B47" s="27" t="str">
         <v>V1.30.0.0</v>
       </c>
-      <c r="C46" s="27" t="str">
+      <c r="C47" s="27" t="str">
         <v>V1.29.0.0</v>
       </c>
-      <c r="D46" s="23" t="str">
+      <c r="D47" s="23" t="str">
         <v>新增水位设置项并
 调整菜单操作</v>
       </c>
-      <c r="E46" s="23" t="str">
+      <c r="E47" s="23" t="str">
         <v>1. 新增“水位滞后时间”设置项。
 2. 进入菜单的长按确认时间改为约 3 秒。
 3. 调整水位等菜单顺序。
 4. 更新液位频率、水位电容和 SI 首点的部分出厂默认值。</v>
       </c>
-      <c r="F46" s="23" t="str">
+      <c r="F47" s="23" t="str">
         <v>水位滞后时间在该版只保存和显示，尚不影响测量。
 两块板需配套；瓦锡兰写参数须使用对应通信格式。</v>
       </c>
     </row>
-    <row r="47" ht="59" customHeight="1">
-      <c r="A47" s="26" t="n">
+    <row r="48" ht="59" customHeight="1">
+      <c r="A48" s="26" t="n">
         <v>46221</v>
       </c>
-      <c r="B47" s="28" t="str">
+      <c r="B48" s="28" t="str">
         <v>V1.29.1.0</v>
       </c>
-      <c r="C47" s="28" t="str">
+      <c r="C48" s="28" t="str">
         <v>V1.28.0.0</v>
       </c>
-      <c r="D47" s="24" t="str">
+      <c r="D48" s="24" t="str">
         <v>修复测量完成后结果
 仍旧或不全</v>
       </c>
-      <c r="E47" s="24" t="str">
+      <c r="E48" s="24" t="str">
         <v>1. 修复已显示测量完成，但测点还是旧数据或没有收齐的问题。
 2. 结果传输失败后可以重试，成功后清除对应传输故障。
 3. 输出调试日志时，减少对正常通信的影响。</v>
       </c>
-      <c r="F47" s="24" t="str">
+      <c r="F48" s="24" t="str">
         <v>该版 20-13 表示结果传输失败；主控实际故障优先
 显示。</v>
       </c>
     </row>
-    <row r="48" ht="74" customHeight="1">
-      <c r="A48" s="25" t="n">
+    <row r="49" ht="74" customHeight="1">
+      <c r="A49" s="25" t="n">
         <v>46220</v>
       </c>
-      <c r="B48" s="27" t="str">
+      <c r="B49" s="27" t="str">
         <v>V1.29.0.0</v>
       </c>
-      <c r="C48" s="27" t="str">
+      <c r="C49" s="27" t="str">
         <v>V1.27.0.0</v>
       </c>
-      <c r="D48" s="23" t="str">
+      <c r="D49" s="23" t="str">
         <v>等待读数时保持电流，
 增加通信统计</v>
       </c>
-      <c r="E48" s="23" t="str">
+      <c r="E49" s="23" t="str">
         <v>1. 重新找液位、切换操作或读数暂未稳定时，保持上次正常过程电流。
 2. 屏幕增加主控通信次数、失败比例和失败原因，方便检查连接。</v>
       </c>
-      <c r="F48" s="23" t="str">
+      <c r="F49" s="23" t="str">
         <v>旧“空高”改为“传感器位置”，旧“非跟随电流”
 改为“初始电流”；两板配套升级后务必核对电流
 设置。</v>
       </c>
     </row>
-    <row r="49" ht="74" customHeight="1">
-      <c r="A49" s="26" t="n">
+    <row r="50" ht="74" customHeight="1">
+      <c r="A50" s="26" t="n">
         <v>46219</v>
       </c>
-      <c r="B49" s="28" t="str">
+      <c r="B50" s="28" t="str">
         <v>V1.28.0.0</v>
       </c>
-      <c r="C49" s="28" t="str">
+      <c r="C50" s="28" t="str">
         <v>V1.26.0.0</v>
       </c>
-      <c r="D49" s="24" t="str">
+      <c r="D50" s="24" t="str">
         <v>增加故障电流选择，
 修复通信提示</v>
       </c>
-      <c r="E49" s="24" t="str">
+      <c r="E50" s="24" t="str">
         <v>1. 电流故障时可选择输出设定的故障电流，或保持上次正常电流。
 2. 修复两块板程序不匹配时一直显示“通信尝试”的问题。
 3. 分布结果传输失败后会退出等待，不再一直显示测量中。
 4. 设备重启后，不继续使用重启前的旧测点。</v>
       </c>
-      <c r="F49" s="24" t="str">
+      <c r="F50" s="24" t="str">
         <v>两块板需配套。电流保持规则在下一版本仍有调整，
 故障编号按对应版本查表。</v>
       </c>
     </row>
-    <row r="50" ht="89" customHeight="1">
-      <c r="A50" s="25" t="n">
+    <row r="51" ht="89" customHeight="1">
+      <c r="A51" s="25" t="n">
         <v>46219</v>
       </c>
-      <c r="B50" s="27" t="str">
+      <c r="B51" s="27" t="str">
         <v>V1.27.0.0</v>
       </c>
-      <c r="C50" s="27" t="str">
+      <c r="C51" s="27" t="str">
         <v>V1.25.0.0</v>
       </c>
-      <c r="D50" s="23" t="str">
+      <c r="D51" s="23" t="str">
         <v>扩展电流输出设置，
 防止混入旧结果</v>
       </c>
-      <c r="E50" s="23" t="str">
+      <c r="E51" s="23" t="str">
         <v>1. 电流输出可设置测量来源、固定电流、变化快慢、故障动作和模拟
    测试。
 2. 修复固定点结果中混入不同次测量数据的问题。
 3. 通信未确认时，不把旧值当本次读数返回。
 4. 自动恢复后，只有真正测量成功才记录“重试成功”。</v>
       </c>
-      <c r="F50" s="23" t="str">
+      <c r="F51" s="23" t="str">
         <v>两块板需配套并核对电流设置。屏幕电流不是电流
 表实测值；瓦锡兰最多输出 100 个测点。</v>
       </c>
     </row>
-    <row r="51" ht="74" customHeight="1">
-      <c r="A51" s="26" t="n">
+    <row r="52" ht="74" customHeight="1">
+      <c r="A52" s="26" t="n">
         <v>46218</v>
       </c>
-      <c r="B51" s="28" t="str">
+      <c r="B52" s="28" t="str">
         <v>V1.26.0.0</v>
       </c>
-      <c r="C51" s="28" t="str">
+      <c r="C52" s="28" t="str">
         <v>V1.24.0.0</v>
       </c>
-      <c r="D51" s="24" t="str">
+      <c r="D52" s="24" t="str">
         <v>修正 SI 完成时机及
 新旧结果混用</v>
       </c>
-      <c r="E51" s="24" t="str">
+      <c r="E52" s="24" t="str">
         <v>1. SI 测完各点后，先回到液面并停稳，再显示测量完成。
 2. 取消或失败时，不把本轮结果当作完整结果。
 3. 修复一次查询中混入新旧测点的问题。
 4. 完善跨日自动测量及站 2 通信兼容。</v>
       </c>
-      <c r="F51" s="24" t="str">
+      <c r="F52" s="24" t="str">
         <v>两块板需配套。旧显示板设置升级保存失败的风险
 在原文中仍未修复，先记录 SI 和串口设置。</v>
       </c>
     </row>
-    <row r="52" ht="59" customHeight="1">
-      <c r="A52" s="25" t="n">
+    <row r="53" ht="59" customHeight="1">
+      <c r="A53" s="25" t="n">
         <v>46217</v>
       </c>
-      <c r="B52" s="27" t="str">
+      <c r="B53" s="27" t="str">
         <v>V1.25.0.0</v>
       </c>
-      <c r="C52" s="27" t="str">
+      <c r="C53" s="27" t="str">
         <v>V1.23.0.0</v>
       </c>
-      <c r="D52" s="23" t="str">
+      <c r="D53" s="23" t="str">
         <v>重新编排故障编号和
 中文原因</v>
       </c>
-      <c r="E52" s="23" t="str">
+      <c r="E53" s="23" t="str">
         <v>1. 按二代设备的部件重新整理故障编号。
 2. 补充中文故障原因，日志与屏幕使用相同名称。
 3. 删除重复或已被更具体原因替代的故障项。</v>
       </c>
-      <c r="F52" s="23" t="str">
+      <c r="F53" s="23" t="str">
         <v>两块板需配套。主控故障按 CPU2 版本查表，显示
 板自身故障按 CPU3 版本查表。</v>
       </c>
     </row>
-    <row r="53" ht="59" customHeight="1">
-      <c r="A53" s="26" t="n">
+    <row r="54" ht="59" customHeight="1">
+      <c r="A54" s="26" t="n">
         <v>46216</v>
       </c>
-      <c r="B53" s="28" t="str">
+      <c r="B54" s="28" t="str">
         <v>V1.24.0.0</v>
       </c>
-      <c r="C53" s="28" t="str">
+      <c r="C54" s="28" t="str">
         <v>V1.22.0.0</v>
       </c>
-      <c r="D53" s="24" t="str">
+      <c r="D54" s="24" t="str">
         <v>新增安全传感器支持
 并兼容旧类型</v>
       </c>
-      <c r="E53" s="24" t="str">
+      <c r="E54" s="24" t="str">
         <v>1. 新增安全传感器的识别、测量和参数读取。
 2. 仍可识别原有 DSM、LTD/V2 传感器。
 3. 传感器不支持某些附加功能时，不再因此阻断原有测量。</v>
       </c>
-      <c r="F53" s="24" t="str">
+      <c r="F54" s="24" t="str">
         <v>退回旧程序前，先改回旧程序支持的传感器类型；
 支持通信不等于通过安全认证。</v>
       </c>
     </row>
-    <row r="54" ht="59" customHeight="1">
-      <c r="A54" s="25" t="n">
+    <row r="55" ht="59" customHeight="1">
+      <c r="A55" s="25" t="n">
         <v>46215</v>
       </c>
-      <c r="B54" s="27" t="str">
+      <c r="B55" s="27" t="str">
         <v>V1.23.0.0</v>
       </c>
-      <c r="C54" s="27" t="str">
+      <c r="C55" s="27" t="str">
         <v>V1.22.0.0</v>
       </c>
-      <c r="D54" s="23" t="str">
+      <c r="D55" s="23" t="str">
         <v>细分故障原因，支持
 远程切换协议</v>
       </c>
-      <c r="E54" s="23" t="str">
+      <c r="E55" s="23" t="str">
         <v>1. 故障原因分类更细，方便区分电机、传感器、存储和电流输出问题。
 2. 减少同一故障反复刷日志。
 3. 可由外部设备切换通信协议，保存失败会提示并恢复原设置。</v>
       </c>
-      <c r="F54" s="23" t="str">
+      <c r="F55" s="23" t="str">
         <v>两块板需配套升级；历史故障需按当时版本查表。</v>
       </c>
     </row>
-    <row r="55" ht="74" customHeight="1">
-      <c r="A55" s="26" t="n">
+    <row r="56" ht="74" customHeight="1">
+      <c r="A56" s="26" t="n">
         <v>46214</v>
       </c>
-      <c r="B55" s="28" t="str">
+      <c r="B56" s="28" t="str">
         <v>V1.22.0.0</v>
       </c>
-      <c r="C55" s="28" t="str">
+      <c r="C56" s="28" t="str">
         <v>V1.21.0.0</v>
       </c>
-      <c r="D55" s="24" t="str">
+      <c r="D56" s="24" t="str">
         <v>支持 LTD 数据及参数
 查询、设置</v>
       </c>
-      <c r="E55" s="24" t="str">
+      <c r="E56" s="24" t="str">
         <v>1. LTD 接口可以查询测量数据、读取和修改参数。
 2. 主控确认接收参数后，才回复修改成功。
 3. 格式不完整或带多余字符的调试命令不会误执行。
 4. 新增停止、版本、状态和故障查询命令。</v>
       </c>
-      <c r="F55" s="24" t="str">
+      <c r="F56" s="24" t="str">
         <v>原来设为 LTD 的端口升级后会开始回复数据，需
 核对上位机设置。</v>
       </c>
     </row>
-    <row r="56" ht="74" customHeight="1">
-      <c r="A56" s="25" t="n">
+    <row r="57" ht="74" customHeight="1">
+      <c r="A57" s="25" t="n">
         <v>46213</v>
       </c>
-      <c r="B56" s="27" t="str">
+      <c r="B57" s="27" t="str">
         <v>V1.21.6.0</v>
       </c>
-      <c r="C56" s="27" t="str">
+      <c r="C57" s="27" t="str">
         <v>V1.20.0.0</v>
       </c>
-      <c r="D56" s="23" t="str">
+      <c r="D57" s="23" t="str">
         <v>修复上电通信等待和
 操作误报成功</v>
       </c>
-      <c r="E56" s="23" t="str">
+      <c r="E57" s="23" t="str">
         <v>1. 修复蓝牙持续收数据时，设备上电一直等待的问题。
 2. 修复传感器低电压回复被误认成编号错误的问题。
 3. 修改参数或发送命令失败时，不再显示成功。
 4. 通信恢复后重新读取设备数据，避免显示断线前的旧数据。</v>
       </c>
-      <c r="F56" s="23" t="str">
+      <c r="F57" s="23" t="str">
         <v>显示“设备忙”时等通信恢复后再操作；批量修改
 失败后，重新读取实际参数确认。</v>
       </c>
     </row>
-    <row r="57" ht="59" customHeight="1">
-      <c r="A57" s="26" t="n">
+    <row r="58" ht="59" customHeight="1">
+      <c r="A58" s="26" t="n">
         <v>46211</v>
       </c>
-      <c r="B57" s="28" t="str">
+      <c r="B58" s="28" t="str">
         <v>V1.21.5.0</v>
       </c>
-      <c r="C57" s="28" t="str">
+      <c r="C58" s="28" t="str">
         <v>V1.19.1.0</v>
       </c>
-      <c r="D57" s="24" t="str">
+      <c r="D58" s="24" t="str">
         <v>电流环重接后自动
 恢复输出</v>
       </c>
-      <c r="E57" s="24" t="str">
+      <c r="E58" s="24" t="str">
         <v>1. 电流环断开后重新接上，设备会定期尝试恢复输出。
 2. 恢复成功后回到有效目标电流，不再继续输出故障电流。
 3. 电流输出故障单独记录，不再由后台检查直接中断整机测量。</v>
       </c>
-      <c r="F57" s="24" t="str">
+      <c r="F58" s="24" t="str">
         <v>电流是否恢复正常，需用仪表实测。</v>
       </c>
     </row>
-    <row r="58" ht="48" customHeight="1">
-      <c r="A58" s="25" t="n">
+    <row r="59" ht="48" customHeight="1">
+      <c r="A59" s="25" t="n">
         <v>46211</v>
       </c>
-      <c r="B58" s="27" t="str">
+      <c r="B59" s="27" t="str">
         <v>V1.21.4.0</v>
       </c>
-      <c r="C58" s="27" t="str">
+      <c r="C59" s="27" t="str">
         <v>V1.19.1.0</v>
       </c>
-      <c r="D58" s="23" t="str">
+      <c r="D59" s="23" t="str">
         <v>修复长距离运行时
 探头越来越慢</v>
       </c>
-      <c r="E58" s="23" t="str">
+      <c r="E59" s="23" t="str">
         <v>1. 修复编码轮方式下，探头长距离分段运行后越来越慢的问题。
 2. 修改速度、恢复速度和切换慢速时，也使用正确的尺带长度。</v>
       </c>
-      <c r="F58" s="23" t="str">
+      <c r="F59" s="23" t="str">
         <v>未增加现场参数。</v>
       </c>
     </row>
-    <row r="59" ht="59" customHeight="1">
-      <c r="A59" s="26" t="n">
+    <row r="60" ht="59" customHeight="1">
+      <c r="A60" s="26" t="n">
         <v>46211</v>
       </c>
-      <c r="B59" s="28" t="str">
+      <c r="B60" s="28" t="str">
         <v>V1.21.3.0</v>
       </c>
-      <c r="C59" s="28" t="str">
+      <c r="C60" s="28" t="str">
         <v>V1.19.1.0</v>
       </c>
-      <c r="D59" s="24" t="str">
+      <c r="D60" s="24" t="str">
         <v>减少液位短时波动
 引起的反复动作</v>
       </c>
-      <c r="E59" s="24" t="str">
+      <c r="E60" s="24" t="str">
         <v>1. 方式 0/1 等液位变化持续一段时间后再动作，减少短时波动影响。
 2. 重新找液位期间，屏幕仍显示跟随状态。
 3. 调整方式 5 固定频率找液位的运行方法。</v>
       </c>
-      <c r="F59" s="24" t="str">
+      <c r="F60" s="24" t="str">
         <v>液位滞后时间只用于方式 0/1，最多按 60 秒；
 连续调速方式的稳定等待为 1 秒。</v>
       </c>
     </row>
-    <row r="60" ht="48" customHeight="1">
-      <c r="A60" s="25" t="n">
+    <row r="61" ht="48" customHeight="1">
+      <c r="A61" s="25" t="n">
         <v>46209</v>
       </c>
-      <c r="B60" s="27" t="str">
+      <c r="B61" s="27" t="str">
         <v>V1.21.2.0</v>
       </c>
-      <c r="C60" s="27" t="str">
+      <c r="C61" s="27" t="str">
         <v>V1.19.1.0</v>
       </c>
-      <c r="D60" s="23" t="str">
+      <c r="D61" s="23" t="str">
         <v>SI 测量完成后自动
 返回液位跟随</v>
       </c>
-      <c r="E60" s="23" t="str">
+      <c r="E61" s="23" t="str">
         <v>1. SI 分布测量成功后，自动找液位并继续跟随。
 2. 测量中途收到新操作时，优先执行新操作。</v>
       </c>
-      <c r="F60" s="23" t="str">
+      <c r="F61" s="23" t="str">
         <v>测量失败或被取消时，不强行覆盖已有命令。</v>
       </c>
     </row>
-    <row r="61" ht="59" customHeight="1">
-      <c r="A61" s="26" t="n">
+    <row r="62" ht="59" customHeight="1">
+      <c r="A62" s="26" t="n">
         <v>46205</v>
       </c>
-      <c r="B61" s="28" t="str">
+      <c r="B62" s="28" t="str">
         <v>V1.21.1.0</v>
       </c>
-      <c r="C61" s="28" t="str">
+      <c r="C62" s="28" t="str">
         <v>V1.19.1.0</v>
       </c>
-      <c r="D61" s="24" t="str">
+      <c r="D62" s="24" t="str">
         <v>修正 SI 测点位置和
 空气点判断</v>
       </c>
-      <c r="E61" s="24" t="str">
+      <c r="E62" s="24" t="str">
         <v>1. 修复 SI 首个测点位置多加了一次罐底位置的问题。
 2. 后续测点按实际位置上报。
 3. 调整空气点的判断顺序，减少误报。</v>
       </c>
-      <c r="F61" s="24" t="str">
+      <c r="F62" s="24" t="str">
         <v>第 0 点对外上报的位置固定为 0。</v>
       </c>
     </row>
-    <row r="62" ht="89" customHeight="1">
-      <c r="A62" s="25" t="n">
+    <row r="63" ht="89" customHeight="1">
+      <c r="A63" s="25" t="n">
         <v>46204</v>
       </c>
-      <c r="B62" s="27" t="str">
+      <c r="B63" s="27" t="str">
         <v>V1.21.0.0</v>
       </c>
-      <c r="C62" s="27" t="str">
+      <c r="C63" s="27" t="str">
         <v>V1.19.0.0</v>
       </c>
-      <c r="D62" s="23" t="str">
+      <c r="D63" s="23" t="str">
         <v>新增独立 SI 分布
 测量及自动测量</v>
       </c>
-      <c r="E62" s="23" t="str">
+      <c r="E63" s="23" t="str">
         <v>1. 新增独立的 SI 分布测量，可设置首点、点间距、停留时间和探底
    频次。
 2. 增加自动分布测量设置，最多测 200 点。
 3. 其他类型的分布结果不再被误当成 SI 结果。
 4. 取消测量后，不把只测了一部分的结果显示为完成。</v>
       </c>
-      <c r="F62" s="23" t="str">
+      <c r="F63" s="23" t="str">
         <v>两块板需配套。SI 返回 -200.00 ℃ 或密度 0 时，
 可能是无效标记，不能当实测值。</v>
       </c>
     </row>
-    <row r="63" ht="59" customHeight="1">
-      <c r="A63" s="26" t="n">
+    <row r="64" ht="59" customHeight="1">
+      <c r="A64" s="26" t="n">
         <v>46204</v>
       </c>
-      <c r="B63" s="28" t="str">
+      <c r="B64" s="28" t="str">
         <v>V1.20.3.0</v>
       </c>
-      <c r="C63" s="28" t="str">
+      <c r="C64" s="28" t="str">
         <v>V1.18.2.0</v>
       </c>
-      <c r="D63" s="24" t="str">
+      <c r="D64" s="24" t="str">
         <v>编码器通信失败后
 自动重试</v>
       </c>
-      <c r="E63" s="24" t="str">
+      <c r="E64" s="24" t="str">
         <v>1. 编码器通信前几次失败时立即重试。
 2. 持续异常不再重复刷日志，但仍继续尝试读取，便于恢复。
 3. 取得正常位置后及时使用，减少上电等待。</v>
       </c>
-      <c r="F63" s="24" t="str">
+      <c r="F64" s="24" t="str">
         <v>持续异常仍按故障处理。</v>
       </c>
     </row>
-    <row r="64" ht="59" customHeight="1">
-      <c r="A64" s="25" t="n">
+    <row r="65" ht="59" customHeight="1">
+      <c r="A65" s="25" t="n">
         <v>46202</v>
       </c>
-      <c r="B64" s="27" t="str">
+      <c r="B65" s="27" t="str">
         <v>V1.20.2.0</v>
       </c>
-      <c r="C64" s="27" t="str">
+      <c r="C65" s="27" t="str">
         <v>V1.18.2.0</v>
       </c>
-      <c r="D64" s="23" t="str">
+      <c r="D65" s="23" t="str">
         <v>减少上电编码器误报
 和蓝牙识别失败</v>
       </c>
-      <c r="E64" s="23" t="str">
+      <c r="E65" s="23" t="str">
         <v>1. 减少编码器刚上电未稳定时的误报。
 2. 过滤传感器上电时的干扰内容，减少蓝牙识别失败。
 3. 增加故障记录，方便区分不同的通信问题。</v>
       </c>
-      <c r="F64" s="23" t="str">
+      <c r="F65" s="23" t="str">
         <v>增加诊断记录不表示接线或硬件故障已排除。</v>
       </c>
     </row>
-    <row r="65" ht="74" customHeight="1">
-      <c r="A65" s="26" t="n">
+    <row r="66" ht="74" customHeight="1">
+      <c r="A66" s="26" t="n">
         <v>46200</v>
       </c>
-      <c r="B65" s="28" t="str">
+      <c r="B66" s="28" t="str">
         <v>V1.20.1.0</v>
       </c>
-      <c r="C65" s="28" t="str">
+      <c r="C66" s="28" t="str">
         <v>V1.18.1.0</v>
       </c>
-      <c r="D65" s="24" t="str">
+      <c r="D66" s="24" t="str">
         <v>修正测点等待时间和
 菜单返回</v>
       </c>
-      <c r="E65" s="24" t="str">
+      <c r="E66" s="24" t="str">
         <v>1. 修复分布测量每点停留时间的单位错误，按设置的秒数等待。
 2. 普通菜单 120 秒无操作，自动回到状态页。
 3. 修正部分菜单返回位置和单位显示。
 4. 参数日志可以查看修改前后的差别。</v>
       </c>
-      <c r="F65" s="24" t="str">
+      <c r="F66" s="24" t="str">
         <v>电机运动监控页和扭力等待页不会按普通菜单超时
 退出。</v>
       </c>
     </row>
-    <row r="66" ht="59" customHeight="1">
-      <c r="A66" s="25" t="n">
+    <row r="67" ht="59" customHeight="1">
+      <c r="A67" s="25" t="n">
         <v>46199</v>
       </c>
-      <c r="B66" s="27" t="str">
+      <c r="B67" s="27" t="str">
         <v>V1.20.0.0</v>
       </c>
-      <c r="C66" s="27" t="str">
+      <c r="C67" s="27" t="str">
         <v>V1.18.0.0</v>
       </c>
-      <c r="D66" s="23" t="str">
+      <c r="D67" s="23" t="str">
         <v>密度显示两位小数，
 保留频率判断的小数</v>
       </c>
-      <c r="E66" s="23" t="str">
+      <c r="E67" s="23" t="str">
         <v>1. 密度读数和相关参数统一显示两位小数。
 2. 修复判断液位频率变化时丢失小数的问题。
 3. 继电器名称统一为 K1～K4，并调整菜单顺序。</v>
       </c>
-      <c r="F66" s="23" t="str">
+      <c r="F67" s="23" t="str">
         <v>两块板需配套升级。旧密度设置会自动换算，外部
 DSM、瓦锡兰、SI 系统的密度单位不变。</v>
       </c>
     </row>
-    <row r="67" ht="74" customHeight="1">
-      <c r="A67" s="26" t="n">
+    <row r="68" ht="74" customHeight="1">
+      <c r="A68" s="26" t="n">
         <v>46199</v>
       </c>
-      <c r="B67" s="28" t="str">
+      <c r="B68" s="28" t="str">
         <v>V1.19.0.0</v>
       </c>
-      <c r="C67" s="28" t="str">
+      <c r="C68" s="28" t="str">
         <v>V1.17.0.0</v>
       </c>
-      <c r="D67" s="24" t="str">
+      <c r="D68" s="24" t="str">
         <v>修复液位、水位标定
 多出 0.1 mm</v>
       </c>
-      <c r="E67" s="24" t="str">
+      <c r="E68" s="24" t="str">
         <v>1. 修复液位、水位标定结果固定多出 0.1 mm 的问题。
 2. 取消“强制提零点”操作。
 3. 可查看蓝牙连接设备地址和电机电流档位。
 4. 统一使用“液位”“扭力”等名称。</v>
       </c>
-      <c r="F67" s="24" t="str">
+      <c r="F68" s="24" t="str">
         <v>瓦锡兰默认通信改为 2400 8E1，旧默认设置会调整；
 旧命令 115 不再执行。</v>
       </c>
     </row>
-    <row r="68" ht="59" customHeight="1">
-      <c r="A68" s="25" t="n">
+    <row r="69" ht="59" customHeight="1">
+      <c r="A69" s="25" t="n">
         <v>46199</v>
       </c>
-      <c r="B68" s="27" t="str">
+      <c r="B69" s="27" t="str">
         <v>V1.18.1.1</v>
       </c>
-      <c r="C68" s="27" t="str">
+      <c r="C69" s="27" t="str">
         <v>V1.16.1.1</v>
       </c>
-      <c r="D68" s="23" t="str">
+      <c r="D69" s="23" t="str">
         <v>新增电流量程与
 正反向输出设置</v>
       </c>
-      <c r="E68" s="23" t="str">
+      <c r="E69" s="23" t="str">
         <v>1. 可以分别设置液位范围和对应电流值。
 2. 支持液位升高时电流增加，或电流降低。
 3. 电流报警和继电器报警可分别设置。</v>
       </c>
-      <c r="F68" s="23" t="str">
+      <c r="F69" s="23" t="str">
         <v>两块板需配套升级；升级后核对电流量程和报警值。</v>
       </c>
     </row>
-    <row r="69" ht="59" customHeight="1">
-      <c r="A69" s="26" t="n">
+    <row r="70" ht="59" customHeight="1">
+      <c r="A70" s="26" t="n">
         <v>46198</v>
       </c>
-      <c r="B69" s="28" t="str">
+      <c r="B70" s="28" t="str">
         <v>V1.18.1.0</v>
       </c>
-      <c r="C69" s="28" t="str">
+      <c r="C70" s="28" t="str">
         <v>V1.16.1.0</v>
       </c>
-      <c r="D69" s="24" t="str">
+      <c r="D70" s="24" t="str">
         <v>修复继电器读数误判，
 息屏设置立即生效</v>
       </c>
-      <c r="E69" s="24" t="str">
+      <c r="E70" s="24" t="str">
         <v>1. 修复液位已恢复正常，继电器却仍认为液位无效的问题。
 2. 还未测得温度时，不把初始 0 值当作真实温度报警。
 3. 息屏开关保存后立即生效，无需重启。</v>
       </c>
-      <c r="F69" s="24" t="str">
+      <c r="F70" s="24" t="str">
         <v>本条描述的是该版本的报警判断方法。</v>
       </c>
     </row>
-    <row r="70" ht="59" customHeight="1">
-      <c r="A70" s="25" t="n">
+    <row r="71" ht="59" customHeight="1">
+      <c r="A71" s="25" t="n">
         <v>46198</v>
       </c>
-      <c r="B70" s="27" t="str">
+      <c r="B71" s="27" t="str">
         <v>V1.18.0.0</v>
       </c>
-      <c r="C70" s="27" t="str">
+      <c r="C71" s="27" t="str">
         <v>V1.16.0.0</v>
       </c>
-      <c r="D70" s="23" t="str">
+      <c r="D71" s="23" t="str">
         <v>修复标零误报及手动
 电流测试干扰</v>
       </c>
-      <c r="E70" s="23" t="str">
+      <c r="E71" s="23" t="str">
         <v>1. 修复重新标零时，探头离开零点误报扭力故障的问题。
 2. 完善电流测试和故障记录。
 3. 修复自动电流更新干扰手动电流测试的问题。</v>
       </c>
-      <c r="F70" s="23" t="str">
+      <c r="F71" s="23" t="str">
         <v>判断实际输出电流，仍需用电流表测量。</v>
       </c>
     </row>
-    <row r="71" ht="74" customHeight="1">
-      <c r="A71" s="26" t="n">
+    <row r="72" ht="74" customHeight="1">
+      <c r="A72" s="26" t="n">
         <v>46197</v>
       </c>
-      <c r="B71" s="28" t="str">
+      <c r="B72" s="28" t="str">
         <v>V1.17.0.0</v>
       </c>
-      <c r="C71" s="28" t="str">
+      <c r="C72" s="28" t="str">
         <v>V1.16.0.0</v>
       </c>
-      <c r="D71" s="24" t="str">
+      <c r="D72" s="24" t="str">
         <v>修复蓝牙查询后的
 通信恢复和菜单返回</v>
       </c>
-      <c r="E71" s="24" t="str">
+      <c r="E72" s="24" t="str">
         <v>1. 统一检查蓝牙主机、从机的连接状态。
 2. 改善查完蓝牙状态后，传感器通信未恢复的问题。
 3. 修复继电器菜单返回到错误页面的问题。
 4. 尺带厚度增加常用材料选项和手工输入。</v>
       </c>
-      <c r="F71" s="24" t="str">
+      <c r="F72" s="24" t="str">
         <v>更换尺带后，核对材料和厚度设置。</v>
       </c>
     </row>
-    <row r="72" ht="59" customHeight="1">
-      <c r="A72" s="25" t="n">
+    <row r="73" ht="59" customHeight="1">
+      <c r="A73" s="25" t="n">
         <v>46197</v>
       </c>
-      <c r="B72" s="27" t="str">
+      <c r="B73" s="27" t="str">
         <v>V1.16.2.0</v>
       </c>
-      <c r="C72" s="27" t="str">
+      <c r="C73" s="27" t="str">
         <v>V1.15.2.0</v>
       </c>
-      <c r="D72" s="23" t="str">
+      <c r="D73" s="23" t="str">
         <v>修复探头接近测点时
 过早停车</v>
       </c>
-      <c r="E72" s="23" t="str">
+      <c r="E73" s="23" t="str">
         <v>1. 单点、固定点和分布测点改为先快后慢地接近目标。
 2. 修复低速阶段过早停车、未到目标的问题。
 3. 瓦锡兰测后回固定点采用同样的定位方法。</v>
       </c>
-      <c r="F72" s="23" t="str">
+      <c r="F73" s="23" t="str">
         <v>该版停稳后偏差超过 10 mm 才报定位异常，这不是
 设备测量精度。</v>
       </c>
     </row>
-    <row r="73" ht="59" customHeight="1">
-      <c r="A73" s="26" t="n">
+    <row r="74" ht="59" customHeight="1">
+      <c r="A74" s="26" t="n">
         <v>46196</v>
       </c>
-      <c r="B73" s="28" t="str">
+      <c r="B74" s="28" t="str">
         <v>V1.16.1.0</v>
       </c>
-      <c r="C73" s="28" t="str">
+      <c r="C74" s="28" t="str">
         <v>V1.15.2.0</v>
       </c>
-      <c r="D73" s="24" t="str">
+      <c r="D74" s="24" t="str">
         <v>修复继电器报警设置
 保存后数值不对</v>
       </c>
-      <c r="E73" s="24" t="str">
+      <c r="E74" s="24" t="str">
         <v>1. 修复屏幕输入的报警上下限，保存到主控板后数值不正确的问题。
 2. 修复报警解除范围等设置保存不正确的问题。
 3. 打印参数时补全报警设置，方便核对。</v>
       </c>
-      <c r="F73" s="24" t="str">
+      <c r="F74" s="24" t="str">
         <v>曾用旧版设置过报警值的设备，应重新读取并核对。</v>
       </c>
     </row>
-    <row r="74" ht="48" customHeight="1">
-      <c r="A74" s="25" t="n">
+    <row r="75" ht="48" customHeight="1">
+      <c r="A75" s="25" t="n">
         <v>46191</v>
       </c>
-      <c r="B74" s="27" t="str">
+      <c r="B75" s="27" t="str">
         <v>V1.16.0.1</v>
       </c>
-      <c r="C74" s="27" t="str">
+      <c r="C75" s="27" t="str">
         <v>V1.15.1.0</v>
       </c>
-      <c r="D74" s="23" t="str">
+      <c r="D75" s="23" t="str">
         <v>修复手动通信设置被
 默认值覆盖</v>
       </c>
-      <c r="E74" s="23" t="str">
+      <c r="E75" s="23" t="str">
         <v>1. 修复手动设置的波特率、校验位等被默认值反复覆盖的问题。
 2. 选好通信协议后，可以单独修改串口设置并保存。</v>
       </c>
-      <c r="F74" s="23" t="str">
+      <c r="F75" s="23" t="str">
         <v>升级通常保留已有合法设置；现场需与连接的主站
 保持一致。</v>
       </c>
     </row>
-    <row r="75" ht="59" customHeight="1">
-      <c r="A75" s="26" t="n">
+    <row r="76" ht="59" customHeight="1">
+      <c r="A76" s="26" t="n">
         <v>46190</v>
       </c>
-      <c r="B75" s="28" t="str">
+      <c r="B76" s="28" t="str">
         <v>V1.16.0.1</v>
       </c>
-      <c r="C75" s="28" t="str">
+      <c r="C76" s="28" t="str">
         <v>V1.15.0.2</v>
       </c>
-      <c r="D75" s="24" t="str">
+      <c r="D76" s="24" t="str">
         <v>可设置日期时间，有
 电池可断电保留</v>
       </c>
-      <c r="E75" s="24" t="str">
+      <c r="E76" s="24" t="str">
         <v>1. 新增屏幕日期和时间设置。
 2. 带时钟电池的显示板可在断电后保留时间。
 3. 旧板没有外部时钟时，仍可正常启动。</v>
       </c>
-      <c r="F75" s="24" t="str">
+      <c r="F76" s="24" t="str">
         <v>断电保时取决于实际硬件和电池，升级后核对日期
 时间。</v>
       </c>
     </row>
-    <row r="76" ht="59" customHeight="1">
-      <c r="A76" s="25" t="n">
+    <row r="77" ht="59" customHeight="1">
+      <c r="A77" s="25" t="n">
         <v>46190</v>
       </c>
-      <c r="B76" s="27" t="str">
+      <c r="B77" s="27" t="str">
         <v>V1.16.0.1</v>
       </c>
-      <c r="C76" s="27" t="str">
+      <c r="C77" s="27" t="str">
         <v>V1.15.0.1</v>
       </c>
-      <c r="D76" s="23" t="str">
+      <c r="D77" s="23" t="str">
         <v>减少屏幕闪烁，修复
 参数显示异常</v>
       </c>
-      <c r="E76" s="23" t="str">
+      <c r="E77" s="23" t="str">
         <v>1. 减少状态页频繁闪烁和读数跳动。
 2. 修复参数范围显示异常、输入文字超出屏幕的问题。
 3. 罐底检测方式只允许选择有效的两种方式。</v>
       </c>
-      <c r="F76" s="23" t="str">
+      <c r="F77" s="23" t="str">
         <v>旧设置中的罐底检测方式不正确时，按扭力方式
 处理。</v>
       </c>
     </row>
-    <row r="77" ht="59" customHeight="1">
-      <c r="A77" s="26" t="n">
+    <row r="78" ht="59" customHeight="1">
+      <c r="A78" s="26" t="n">
         <v>46188</v>
       </c>
-      <c r="B77" s="28" t="str">
+      <c r="B78" s="28" t="str">
         <v>V1.16.0.0</v>
       </c>
-      <c r="C77" s="28" t="str">
+      <c r="C78" s="28" t="str">
         <v>V1.15.0.0</v>
       </c>
-      <c r="D77" s="24" t="str">
+      <c r="D78" s="24" t="str">
         <v>新增电流输出开关和
 状态显示</v>
       </c>
-      <c r="E77" s="24" t="str">
+      <c r="E78" s="24" t="str">
         <v>1. 新增电流输出开关。
 2. 屏幕可查看电流输出状态和相关故障。
 3. 整理液位对应电流的计算和测试功能。</v>
       </c>
-      <c r="F77" s="24" t="str">
+      <c r="F78" s="24" t="str">
         <v>两块板需配套升级。旧版升级后电流输出默认关闭，
 使用前需检查开关和接线。</v>
       </c>
     </row>
-    <row r="78" ht="59" customHeight="1">
-      <c r="A78" s="25" t="n">
+    <row r="79" ht="59" customHeight="1">
+      <c r="A79" s="25" t="n">
         <v>46186</v>
       </c>
-      <c r="B78" s="27" t="str">
+      <c r="B79" s="27" t="str">
         <v>V1.15.0.0</v>
       </c>
-      <c r="C78" s="27" t="str">
+      <c r="C79" s="27" t="str">
         <v>V1.14.0.0</v>
       </c>
-      <c r="D78" s="23" t="str">
+      <c r="D79" s="23" t="str">
         <v>新增蓝牙信号显示，
 调整测量菜单</v>
       </c>
-      <c r="E78" s="23" t="str">
+      <c r="E79" s="23" t="str">
         <v>1. 读取部件参数时可以查看蓝牙信号强度。
 2. 重新整理测量和探头运动菜单，方便查找。
 3. 修复瓦锡兰测量时，把异常频率误当空气点的问题。</v>
       </c>
-      <c r="F78" s="23" t="str">
+      <c r="F79" s="23" t="str">
         <v>需配套升级两块板。没有信号读数时显示 N/A，
 查询失败不会重新配对。</v>
       </c>
     </row>
-    <row r="79" ht="48" customHeight="1">
-      <c r="A79" s="26" t="n">
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="26" t="n">
         <v>46186</v>
       </c>
-      <c r="B79" s="28" t="str">
+      <c r="B80" s="28" t="str">
         <v>V1.14.0.1</v>
       </c>
-      <c r="C79" s="28" t="str">
+      <c r="C80" s="28" t="str">
         <v>V1.13.0.0</v>
       </c>
-      <c r="D79" s="24" t="str">
+      <c r="D80" s="24" t="str">
         <v>统一移动目标检查和
 停车后位置更新</v>
       </c>
-      <c r="E79" s="24" t="str">
+      <c r="E80" s="24" t="str">
         <v>1. 统一普通移动和点动的目标位置检查。
 2. 统一停车后的位置更新，以及变速后恢复原速度的处理。</v>
       </c>
-      <c r="F79" s="24" t="str">
+      <c r="F80" s="24" t="str">
         <v>未增加现场参数，原测试命令不变。</v>
       </c>
     </row>
-    <row r="80" ht="59" customHeight="1">
-      <c r="A80" s="25" t="n">
+    <row r="81" ht="59" customHeight="1">
+      <c r="A81" s="25" t="n">
         <v>46185</v>
       </c>
-      <c r="B80" s="27" t="str">
+      <c r="B81" s="27" t="str">
         <v>V1.14.0.0</v>
       </c>
-      <c r="C80" s="27" t="str">
+      <c r="C81" s="27" t="str">
         <v>V1.13.0.0</v>
       </c>
-      <c r="D80" s="23" t="str">
+      <c r="D81" s="23" t="str">
         <v>新增三种找液位方式，
 调整找水位动作</v>
       </c>
-      <c r="E80" s="23" t="str">
+      <c r="E81" s="23" t="str">
         <v>1. 增加三种连续找液位方式：按密度、按相对频率、按固定频率。
 2. 屏幕增加相应选项。
 3. 找水位时，若探头已在水中，先向上离开水层，再低速向下寻找。</v>
       </c>
-      <c r="F80" s="23" t="str">
+      <c r="F81" s="23" t="str">
         <v>两块板需配套升级；方式 3“超声”仍未启用。</v>
       </c>
     </row>
-    <row r="81" ht="48" customHeight="1">
-      <c r="A81" s="26" t="n">
+    <row r="82" ht="48" customHeight="1">
+      <c r="A82" s="26" t="n">
         <v>46184</v>
       </c>
-      <c r="B81" s="28" t="str">
+      <c r="B82" s="28" t="str">
         <v>V1.13.2.0</v>
       </c>
-      <c r="C81" s="28" t="str">
+      <c r="C82" s="28" t="str">
         <v>V1.12.1.0</v>
       </c>
-      <c r="D81" s="24" t="str">
+      <c r="D82" s="24" t="str">
         <v>阻止越界移动和参数
 错误后的反复重测</v>
       </c>
-      <c r="E81" s="24" t="str">
+      <c r="E82" s="24" t="str">
         <v>1. 普通移动和点动都会先检查目标位置，超出允许范围时不启动。
 2. 参数设置错误时，不再反复自动重测。</v>
       </c>
-      <c r="F81" s="24" t="str">
+      <c r="F82" s="24" t="str">
         <v>先修正位置、罐高等设置，再重新发起测量。</v>
       </c>
     </row>
-    <row r="82" ht="74" customHeight="1">
-      <c r="A82" s="25" t="n">
+    <row r="83" ht="74" customHeight="1">
+      <c r="A83" s="25" t="n">
         <v>46184</v>
       </c>
-      <c r="B82" s="27" t="str">
+      <c r="B83" s="27" t="str">
         <v>V1.13.1.0</v>
       </c>
-      <c r="C82" s="27" t="str">
+      <c r="C83" s="27" t="str">
         <v>V1.12.1.0</v>
       </c>
-      <c r="D82" s="23" t="str">
+      <c r="D83" s="23" t="str">
         <v>修正瓦锡兰空气点
 判断及失败结果保留</v>
       </c>
-      <c r="E82" s="23" t="str">
+      <c r="E83" s="23" t="str">
         <v>1. 调整测点间移动和空气点判断，避免将空气中的读数算入液体结果。
 2. 遇到空气点后，重新寻找液面。
 3. 本轮测量失败时，保留上次完整结果，避免结果被清零或只剩部分测
    点。</v>
       </c>
-      <c r="F82" s="23" t="str">
+      <c r="F83" s="23" t="str">
         <v>空气点判断在后续版本中仍有调整。</v>
       </c>
     </row>
-    <row r="83" ht="59" customHeight="1">
-      <c r="A83" s="26" t="n">
+    <row r="84" ht="59" customHeight="1">
+      <c r="A84" s="26" t="n">
         <v>46184</v>
       </c>
-      <c r="B83" s="28" t="str">
+      <c r="B84" s="28" t="str">
         <v>V1.13.0.1</v>
       </c>
-      <c r="C83" s="28" t="str">
+      <c r="C84" s="28" t="str">
         <v>V1.12.1.0</v>
       </c>
-      <c r="D83" s="24" t="str">
+      <c r="D84" s="24" t="str">
         <v>修复长按确认不灵敏
 和确认页误跳过</v>
       </c>
-      <c r="E83" s="24" t="str">
+      <c r="E84" s="24" t="str">
         <v>1. 改善长按确认不灵敏的问题。
 2. 修复先按其他键，再长按确认无法进入菜单的问题。
 3. 长按后需松手再确认，避免不小心跳过确认页。</v>
       </c>
-      <c r="F83" s="24" t="str">
+      <c r="F84" s="24" t="str">
         <v>该版长按时间约 1.5 秒，后续改回约 3 秒。</v>
       </c>
     </row>
-    <row r="84" ht="59" customHeight="1">
-      <c r="A84" s="25" t="n">
+    <row r="85" ht="59" customHeight="1">
+      <c r="A85" s="25" t="n">
         <v>46184</v>
       </c>
-      <c r="B84" s="27" t="str">
+      <c r="B85" s="27" t="str">
         <v>V1.13.0.1</v>
       </c>
-      <c r="C84" s="27" t="str">
+      <c r="C85" s="27" t="str">
         <v>V1.12.0.0</v>
       </c>
-      <c r="D84" s="23" t="str">
+      <c r="D85" s="23" t="str">
         <v>新增五挡亮度，修复
 显示恢复后的乱码</v>
       </c>
-      <c r="E84" s="23" t="str">
+      <c r="E85" s="23" t="str">
         <v>1. 新增五挡屏幕亮度设置。
 2. 修复退出菜单或恢复显示后可能留下乱码的问题。
 3. 读数变化时短暂反白显示，方便查看。</v>
       </c>
-      <c r="F84" s="23" t="str">
+      <c r="F85" s="23" t="str">
         <v>旧显示、通信设置正常保留，亮度默认“中低”。</v>
       </c>
     </row>
-    <row r="85" ht="48" customHeight="1">
-      <c r="A85" s="26" t="n">
+    <row r="86" ht="48" customHeight="1">
+      <c r="A86" s="26" t="n">
         <v>46184</v>
       </c>
-      <c r="B85" s="28" t="str">
+      <c r="B86" s="28" t="str">
         <v>V1.13.0.0</v>
       </c>
-      <c r="C85" s="28" t="str">
+      <c r="C86" s="28" t="str">
         <v>V1.11.2.0</v>
       </c>
-      <c r="D85" s="24" t="str">
+      <c r="D86" s="24" t="str">
         <v>新增长距离与指定
 位置移动测试</v>
       </c>
-      <c r="E85" s="24" t="str">
+      <c r="E86" s="24" t="str">
         <v>1. 新增长距离移动和移动到指定位置的测试命令。
 2. 接近目标时提前减速、停车，停稳后偏差过大会报错。</v>
       </c>
-      <c r="F85" s="24" t="str">
+      <c r="F86" s="24" t="str">
         <v>通过调试串口使用 BJ/BJP 命令。</v>
       </c>
     </row>
-    <row r="86" ht="59" customHeight="1">
-      <c r="A86" s="25" t="n">
+    <row r="87" ht="59" customHeight="1">
+      <c r="A87" s="25" t="n">
         <v>46184</v>
       </c>
-      <c r="B86" s="27" t="str">
+      <c r="B87" s="27" t="str">
         <v>V1.12.2.0</v>
       </c>
-      <c r="C86" s="27" t="str">
+      <c r="C87" s="27" t="str">
         <v>V1.11.2.0</v>
       </c>
-      <c r="D86" s="23" t="str">
+      <c r="D87" s="23" t="str">
         <v>部件参数持续刷新，
 避免混入旧读数</v>
       </c>
-      <c r="E86" s="23" t="str">
+      <c r="E87" s="23" t="str">
         <v>1. 读取完成后，每秒继续更新部件参数，方便观察变化。
 2. 屏幕显示本次读数，不再混入其他测量的旧结果。
 3. 修正通过 DSM 接口读取角度和水电容的结果。</v>
       </c>
-      <c r="F86" s="23" t="str">
+      <c r="F87" s="23" t="str">
         <v>旧接口中名为“水位传感器电压”的项目，实际
 返回水电容。</v>
       </c>
     </row>
-    <row r="87" ht="48" customHeight="1">
-      <c r="A87" s="26" t="n">
+    <row r="88" ht="48" customHeight="1">
+      <c r="A88" s="26" t="n">
         <v>46183</v>
       </c>
-      <c r="B87" s="28" t="str">
+      <c r="B88" s="28" t="str">
         <v>V1.12.1.3</v>
       </c>
-      <c r="C87" s="28" t="str">
+      <c r="C88" s="28" t="str">
         <v>V1.11.1.4</v>
       </c>
-      <c r="D87" s="24" t="str">
+      <c r="D88" s="24" t="str">
         <v>恢复磁通量菜单名称
 并补充选项说明</v>
       </c>
-      <c r="E87" s="24" t="str">
+      <c r="E88" s="24" t="str">
         <v>1. 将“密度修正、温度修正”恢复为“磁通量D、磁通量T”。
 2. 补充菜单各选项的含义。</v>
       </c>
-      <c r="F87" s="24" t="str">
+      <c r="F88" s="24" t="str">
         <v>只是名称变化，参数作用不变。</v>
       </c>
     </row>
-    <row r="88" ht="74" customHeight="1">
-      <c r="A88" s="25" t="n">
+    <row r="89" ht="74" customHeight="1">
+      <c r="A89" s="25" t="n">
         <v>46183</v>
       </c>
-      <c r="B88" s="27" t="str">
+      <c r="B89" s="27" t="str">
         <v>V1.12.1.3</v>
       </c>
-      <c r="C88" s="27" t="str">
+      <c r="C89" s="27" t="str">
         <v>V1.11.1.3</v>
       </c>
-      <c r="D88" s="23" t="str">
+      <c r="D89" s="23" t="str">
         <v>调整出厂设置并增加
 状态页信息</v>
       </c>
-      <c r="E88" s="23" t="str">
+      <c r="E89" s="23" t="str">
         <v>1. 调整 9 项出厂默认设置。
 2. 读取部件参数后，可同时显示频率、电容等读数。
 3. 故障状态增加中文原因。
 4. 修正瓦锡兰测量过程中的显示项目。</v>
       </c>
-      <c r="F88" s="23" t="str">
+      <c r="F89" s="23" t="str">
         <v>已有设置通常保留；旧水位滞后电容阈值为 0 时会
 补默认值。</v>
       </c>
     </row>
-    <row r="89" ht="59" customHeight="1">
-      <c r="A89" s="26" t="n">
+    <row r="90" ht="59" customHeight="1">
+      <c r="A90" s="26" t="n">
         <v>46182</v>
       </c>
-      <c r="B89" s="28" t="str">
+      <c r="B90" s="28" t="str">
         <v>V1.12.1.2</v>
       </c>
-      <c r="C89" s="28" t="str">
+      <c r="C90" s="28" t="str">
         <v>V1.11.1.2</v>
       </c>
-      <c r="D89" s="24" t="str">
+      <c r="D90" s="24" t="str">
         <v>修复参数显示和
 大数值保存错误</v>
       </c>
-      <c r="E89" s="24" t="str">
+      <c r="E90" s="24" t="str">
         <v>1. 补齐速度、频率、电容等设置的单位。
 2. 修正频率小数位和手输密度范围显示。
 3. 修复手工输入较大数值后，保存值变小或不完整的问题。</v>
       </c>
-      <c r="F89" s="24" t="str">
+      <c r="F90" s="24" t="str">
         <v>该版显示板的显示、通信设置会恢复默认，升级后
 需重设；主控测量参数不因本项清空。</v>
       </c>
     </row>
-    <row r="90" ht="48" customHeight="1">
-      <c r="A90" s="25" t="n">
+    <row r="91" ht="48" customHeight="1">
+      <c r="A91" s="25" t="n">
         <v>46182</v>
       </c>
-      <c r="B90" s="27" t="str">
+      <c r="B91" s="27" t="str">
         <v>V1.12.1.2</v>
       </c>
-      <c r="C90" s="27" t="str">
+      <c r="C91" s="27" t="str">
         <v>V1.11.1.1</v>
       </c>
-      <c r="D90" s="23" t="str">
+      <c r="D91" s="23" t="str">
         <v>报警单位随所选测量
 项目变化</v>
       </c>
-      <c r="E90" s="23" t="str">
+      <c r="E91" s="23" t="str">
         <v>1. 报警值的单位随所选测量项目变化，位置用 mm，温度用 ℃。</v>
       </c>
-      <c r="F90" s="23" t="str">
+      <c r="F91" s="23" t="str">
         <v>只改单位显示，不改实际报警值。</v>
       </c>
     </row>
-    <row r="91" ht="59" customHeight="1">
-      <c r="A91" s="26" t="n">
+    <row r="92" ht="59" customHeight="1">
+      <c r="A92" s="26" t="n">
         <v>46182</v>
       </c>
-      <c r="B91" s="28" t="str">
+      <c r="B92" s="28" t="str">
         <v>V1.12.1.2</v>
       </c>
-      <c r="C91" s="28" t="str">
+      <c r="C92" s="28" t="str">
         <v>V1.11.1.0</v>
       </c>
-      <c r="D91" s="24" t="str">
+      <c r="D92" s="24" t="str">
         <v>调整出厂参数，
 瓦锡兰默认不探底</v>
       </c>
-      <c r="E91" s="24" t="str">
+      <c r="E92" s="24" t="str">
         <v>1. 调整 11 项出厂默认设置，涉及自动回零、扭力、盲区和分布测量
    等。
 2. 瓦锡兰探底间隔默认设为 0，表示不探底。</v>
       </c>
-      <c r="F91" s="24" t="str">
+      <c r="F92" s="24" t="str">
         <v>正常升级通常保留现场设置，恢复出厂时才使用新
 默认值。</v>
       </c>
     </row>
-    <row r="92" ht="48" customHeight="1">
-      <c r="A92" s="25" t="n">
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="25" t="n">
         <v>46182</v>
       </c>
-      <c r="B92" s="27" t="str">
+      <c r="B93" s="27" t="str">
         <v>V1.12.1.1</v>
       </c>
-      <c r="C92" s="27" t="str">
+      <c r="C93" s="27" t="str">
         <v>V1.11.1.0</v>
       </c>
-      <c r="D92" s="23" t="str">
+      <c r="D93" s="23" t="str">
         <v>统一程序版本和设备
 信息显示格式</v>
       </c>
-      <c r="E92" s="23" t="str">
+      <c r="E93" s="23" t="str">
         <v>1. 程序版本统一显示为 Vx.x.x.x，便于报修时记录。
 2. 整理设备信息的名称和数字格式，减少显示不全。</v>
       </c>
-      <c r="F92" s="23" t="str">
+      <c r="F93" s="23" t="str">
         <v>只改显示，不改参数实际值。</v>
       </c>
     </row>
-    <row r="93" ht="74" customHeight="1">
-      <c r="A93" s="26" t="n">
+    <row r="94" ht="74" customHeight="1">
+      <c r="A94" s="26" t="n">
         <v>46182</v>
       </c>
-      <c r="B93" s="28" t="str">
+      <c r="B94" s="28" t="str">
         <v>V1.12.1.1</v>
       </c>
-      <c r="C93" s="28" t="str">
+      <c r="C94" s="28" t="str">
         <v>V1.11.0.0</v>
       </c>
-      <c r="D93" s="24" t="str">
+      <c r="D94" s="24" t="str">
         <v>重新分类菜单并增加
 关键参数确认</v>
       </c>
-      <c r="E93" s="24" t="str">
+      <c r="E94" s="24" t="str">
         <v>1. 按测量、输出、通信、显示和维护重新整理菜单。
 2. 修改关键参数前增加确认，减少误操作。
 3. 可查看继电器报警状态。
 4. 修复状态页混入旧结果和文字超出屏幕的问题。</v>
       </c>
-      <c r="F93" s="24" t="str">
+      <c r="F94" s="24" t="str">
         <v>该版修改通信设置会重新套用默认值，后续版本已
 调整。</v>
       </c>
     </row>
-    <row r="94" ht="48" customHeight="1">
-      <c r="A94" s="25" t="n">
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="25" t="n">
         <v>46182</v>
       </c>
-      <c r="B94" s="27" t="str">
+      <c r="B95" s="27" t="str">
         <v>V1.12.1.0</v>
       </c>
-      <c r="C94" s="27" t="str">
+      <c r="C95" s="27" t="str">
         <v>V1.10.1.0</v>
       </c>
-      <c r="D94" s="23" t="str">
+      <c r="D95" s="23" t="str">
         <v>修复停机等待和旧
 动作残留</v>
       </c>
-      <c r="E94" s="23" t="str">
+      <c r="E95" s="23" t="str">
         <v>1. 修复电机已停稳，程序却一直等待的问题。
 2. 修复重新启动后可能继续跑向旧目标的问题。</v>
       </c>
-      <c r="F94" s="23" t="str">
+      <c r="F95" s="23" t="str">
         <v>正常运动时仍会检查是否到达目标。</v>
       </c>
     </row>
-    <row r="95" ht="48" customHeight="1">
-      <c r="A95" s="26" t="n">
+    <row r="96" ht="48" customHeight="1">
+      <c r="A96" s="26" t="n">
         <v>46181</v>
       </c>
-      <c r="B95" s="28" t="str">
+      <c r="B96" s="28" t="str">
         <v>V1.12.0.2</v>
       </c>
-      <c r="C95" s="28" t="str">
+      <c r="C96" s="28" t="str">
         <v>V1.10.1.0</v>
       </c>
-      <c r="D95" s="24" t="str">
+      <c r="D96" s="24" t="str">
         <v>开关和模式改用文字
 选项设置</v>
       </c>
-      <c r="E95" s="24" t="str">
+      <c r="E96" s="24" t="str">
         <v>1. 开关、模式等设置可用上下键选择文字选项。
 2. 进入选择页时，自动选中当前设置。</v>
       </c>
-      <c r="F95" s="24" t="str">
+      <c r="F96" s="24" t="str">
         <v>设置的含义不变，主要是操作更直观。</v>
       </c>
     </row>
-    <row r="96" ht="59" customHeight="1">
-      <c r="A96" s="25" t="n">
+    <row r="97" ht="59" customHeight="1">
+      <c r="A97" s="25" t="n">
         <v>46181</v>
       </c>
-      <c r="B96" s="27" t="str">
+      <c r="B97" s="27" t="str">
         <v>V1.12.0.2</v>
       </c>
-      <c r="C96" s="27" t="str">
+      <c r="C97" s="27" t="str">
         <v>V1.10.0.2</v>
       </c>
-      <c r="D96" s="23" t="str">
+      <c r="D97" s="23" t="str">
         <v>电机通信失败时不再
 误判已停车</v>
       </c>
-      <c r="E96" s="23" t="str">
+      <c r="E97" s="23" t="str">
         <v>1. 修复读不到电机状态时，被误认为电机已停止的问题。
 2. 电机通信失败时保留具体故障原因。
 3. 统一继电器报警菜单名称。</v>
       </c>
-      <c r="F96" s="23" t="str">
+      <c r="F97" s="23" t="str">
         <v>通信出错不会再被“已停止”状态掩盖。</v>
       </c>
     </row>
-    <row r="97" ht="59" customHeight="1">
-      <c r="A97" s="26" t="n">
+    <row r="98" ht="59" customHeight="1">
+      <c r="A98" s="26" t="n">
         <v>46179</v>
       </c>
-      <c r="B97" s="28" t="str">
+      <c r="B98" s="28" t="str">
         <v>V1.12.0.0</v>
       </c>
-      <c r="C97" s="28" t="str">
+      <c r="C98" s="28" t="str">
         <v>V1.10.0.0</v>
       </c>
-      <c r="D97" s="24" t="str">
+      <c r="D98" s="24" t="str">
         <v>新增四路继电器报警
 设置</v>
       </c>
-      <c r="E97" s="24" t="str">
+      <c r="E98" s="24" t="str">
         <v>1. 新增四路继电器报警设置，屏幕可设置报警来源及上下限。
 2. 支持设置报警解除条件、接点形式，以及报警后是否保持。
 3. 原有 DO 报警设置改为新的继电器菜单。</v>
       </c>
-      <c r="F97" s="24" t="str">
+      <c r="F98" s="24" t="str">
         <v>从 CPU2 V1.11.0.1 及更早升级会恢复出厂参数，
 务必先备份。两块板需配套；第四路能否接线使用
 须核对实际硬件。</v>
       </c>
     </row>
-    <row r="98" ht="59" customHeight="1">
-      <c r="A98" s="25" t="n">
+    <row r="99" ht="59" customHeight="1">
+      <c r="A99" s="25" t="n">
         <v>46177</v>
       </c>
-      <c r="B98" s="27" t="str">
+      <c r="B99" s="27" t="str">
         <v>V1.11.0.0</v>
       </c>
-      <c r="C98" s="27" t="str">
+      <c r="C99" s="27" t="str">
         <v>V1.9.0.0</v>
       </c>
-      <c r="D98" s="23" t="str">
+      <c r="D99" s="23" t="str">
         <v>往返测试可调速，
 改善复位后的启动</v>
       </c>
-      <c r="E98" s="23" t="str">
+      <c r="E99" s="23" t="str">
         <v>1. BE 往返测试可以设置速度和加减速快慢。
 2. 修复往返测试范围逐次向下移动的问题。
 3. 改善电机断电、复位后一直提示“电机被禁止”的情况。</v>
       </c>
-      <c r="F98" s="23" t="str">
+      <c r="F99" s="23" t="str">
         <v>速度单位为米/分钟，旧测试命令仍可使用。</v>
       </c>
     </row>
-    <row r="99" ht="74" customHeight="1">
-      <c r="A99" s="26" t="n">
+    <row r="100" ht="74" customHeight="1">
+      <c r="A100" s="26" t="n">
         <v>46176</v>
       </c>
-      <c r="B99" s="28" t="str">
+      <c r="B100" s="28" t="str">
         <v>V1.10.0.0</v>
       </c>
-      <c r="C99" s="28" t="str">
+      <c r="C100" s="28" t="str">
         <v>V1.9.0.0</v>
       </c>
-      <c r="D99" s="24" t="str">
+      <c r="D100" s="24" t="str">
         <v>清除上电旧动作，可
 设置自动恢复次数</v>
       </c>
-      <c r="E99" s="24" t="str">
+      <c r="E100" s="24" t="str">
         <v>1. 上电先清除上次遗留的运动，避免继续执行旧动作。
 2. 位置尚未确定时，不启动普通运动。
 3. 新增“调试模式中”显示和“自动恢复次数”设置。
 4. 修复负空载扭力显示为异常大数的问题。</v>
       </c>
-      <c r="F99" s="24" t="str">
+      <c r="F100" s="24" t="str">
         <v>两块板需配套升级。恢复次数默认 3，设为 0 时不
 自动重新测量。</v>
       </c>
     </row>
-    <row r="100" ht="59" customHeight="1">
-      <c r="A100" s="25" t="n">
+    <row r="101" ht="59" customHeight="1">
+      <c r="A101" s="25" t="n">
         <v>46175</v>
       </c>
-      <c r="B100" s="27" t="str">
+      <c r="B101" s="27" t="str">
         <v>V1.9.1.0</v>
       </c>
-      <c r="C100" s="27" t="str">
+      <c r="C101" s="27" t="str">
         <v>V1.8.0.0</v>
       </c>
-      <c r="D100" s="23" t="str">
+      <c r="D101" s="23" t="str">
         <v>测量前拦截超出允许
 范围的目标位置</v>
       </c>
-      <c r="E100" s="23" t="str">
+      <c r="E101" s="23" t="str">
         <v>1. 测量前先检查目标位置，超出零点或进入罐底盲区时，不再让探头
    继续移动。
 2. 瓦锡兰测后回固定点也会检查目标位置。</v>
       </c>
-      <c r="F100" s="23" t="str">
+      <c r="F101" s="23" t="str">
         <v>提示参数超限时，核对测点位置、罐高和盲区。</v>
       </c>
     </row>
-    <row r="101" ht="48" customHeight="1">
-      <c r="A101" s="26" t="n">
+    <row r="102" ht="48" customHeight="1">
+      <c r="A102" s="26" t="n">
         <v>46175</v>
       </c>
-      <c r="B101" s="28" t="str">
+      <c r="B102" s="28" t="str">
         <v>V1.9.0.0</v>
       </c>
-      <c r="C101" s="28" t="str">
+      <c r="C102" s="28" t="str">
         <v>V1.8.0.0</v>
       </c>
-      <c r="D101" s="24" t="str">
+      <c r="D102" s="24" t="str">
         <v>适配 DSM V1.228
 通信与查询</v>
       </c>
-      <c r="E101" s="24" t="str">
+      <c r="E102" s="24" t="str">
         <v>1. 增加与 DSM V1.228 的通信兼容。
 2. 修正设备状态、命令及参数查询的返回内容。</v>
       </c>
-      <c r="F101" s="24" t="str">
+      <c r="F102" s="24" t="str">
         <v>部分新增查询项只返回 0，不表示对应功能已经
 可用。</v>
       </c>
     </row>
-    <row r="102" ht="59" customHeight="1">
-      <c r="A102" s="25" t="n">
+    <row r="103" ht="59" customHeight="1">
+      <c r="A103" s="25" t="n">
         <v>46165</v>
       </c>
-      <c r="B102" s="27" t="str">
+      <c r="B103" s="27" t="str">
         <v>V1.9.0.0</v>
       </c>
-      <c r="C102" s="27" t="str">
+      <c r="C103" s="27" t="str">
         <v>V1.7.0.0</v>
       </c>
-      <c r="D102" s="23" t="str">
+      <c r="D103" s="23" t="str">
         <v>新增屏幕无线滑环
 匹配操作</v>
       </c>
-      <c r="E102" s="23" t="str">
+      <c r="E103" s="23" t="str">
         <v>1. 屏幕新增“匹配无线滑环”，可自动选择附近信号较强的设备。
 2. 显示匹配进度、结果和连接设备地址。
 3. 增加匹配条件，减少连接到其他设备的情况。</v>
       </c>
-      <c r="F102" s="23" t="str">
+      <c r="F103" s="23" t="str">
         <v>该版固定点监测默认用样机模拟读数，不能将其
 温度和密度当作实测值。</v>
       </c>
     </row>
-    <row r="103" ht="59" customHeight="1">
-      <c r="A103" s="26" t="n">
+    <row r="104" ht="59" customHeight="1">
+      <c r="A104" s="26" t="n">
         <v>46165</v>
       </c>
-      <c r="B103" s="28" t="str">
+      <c r="B104" s="28" t="str">
         <v>V1.8.1.0</v>
       </c>
-      <c r="C103" s="28" t="str">
+      <c r="C104" s="28" t="str">
         <v>V1.6.0.0</v>
       </c>
-      <c r="D103" s="24" t="str">
+      <c r="D104" s="24" t="str">
         <v>修复往返测试启动和
 换向误判</v>
       </c>
-      <c r="E103" s="24" t="str">
+      <c r="E104" s="24" t="str">
         <v>1. 调整 B/BE 测试，减少旧故障状态对测试启动的影响。
 2. 修复电机换向瞬间被误判已停稳的问题。
 3. 测试时按实际传感器类型检查通信。</v>
       </c>
-      <c r="F103" s="24" t="str">
+      <c r="F104" s="24" t="str">
         <v>这是专用调试功能，部分检查少于正式测量，不能
 当正常测量使用。</v>
       </c>
     </row>
-    <row r="104" ht="59" customHeight="1">
-      <c r="A104" s="25" t="n">
+    <row r="105" ht="59" customHeight="1">
+      <c r="A105" s="25" t="n">
         <v>46158</v>
       </c>
-      <c r="B104" s="27" t="str">
+      <c r="B105" s="27" t="str">
         <v>V1.8.0.0</v>
       </c>
-      <c r="C104" s="27" t="str">
+      <c r="C105" s="27" t="str">
         <v>V1.6.0.0</v>
       </c>
-      <c r="D104" s="23" t="str">
+      <c r="D105" s="23" t="str">
         <v>新增 SI 通信及测量
 结果查询</v>
       </c>
-      <c r="E104" s="23" t="str">
+      <c r="E105" s="23" t="str">
         <v>1. 新增 SI 通信，可读取结果、完成时间和设备状态。
 2. 不支持的命令不再回复成功。
 3. 修复读取分布结果时带入上一次测点的问题。</v>
       </c>
-      <c r="F104" s="23" t="str">
+      <c r="F105" s="23" t="str">
         <v>两块板需配套升级。原文此条日期早于上一条，表
 中保留原日期。</v>
       </c>
     </row>
-    <row r="105" ht="59" customHeight="1">
-      <c r="A105" s="26" t="n">
+    <row r="106" ht="59" customHeight="1">
+      <c r="A106" s="26" t="n">
         <v>46161</v>
       </c>
-      <c r="B105" s="28" t="str">
+      <c r="B106" s="28" t="str">
         <v>V1.7.3.0</v>
       </c>
-      <c r="C105" s="28" t="str">
+      <c r="C106" s="28" t="str">
         <v>V1.5.0.0</v>
       </c>
-      <c r="D105" s="24" t="str">
+      <c r="D106" s="24" t="str">
         <v>增加探底超程停机，
 修复回零碰撞误报</v>
       </c>
-      <c r="E105" s="24" t="str">
+      <c r="E106" s="24" t="str">
         <v>1. 探底超过允许下行长度仍未找到罐底时，停机并报错。
 2. 接近罐底时降低速度。
 3. 修复正常到达零点时误报碰撞的问题。</v>
       </c>
-      <c r="F105" s="24" t="str">
+      <c r="F106" s="24" t="str">
         <v>先核对罐高和最大下行距离设置。</v>
       </c>
     </row>
-    <row r="106" ht="74" customHeight="1">
-      <c r="A106" s="25" t="n">
+    <row r="107" ht="74" customHeight="1">
+      <c r="A107" s="25" t="n">
         <v>46158</v>
       </c>
-      <c r="B106" s="27" t="str">
+      <c r="B107" s="27" t="str">
         <v>V1.7.2.0</v>
       </c>
-      <c r="C106" s="27" t="str">
+      <c r="C107" s="27" t="str">
         <v>V1.5.0.0</v>
       </c>
-      <c r="D106" s="23" t="str">
+      <c r="D107" s="23" t="str">
         <v>液位校正后立即刷新，
 修复负数显示</v>
       </c>
-      <c r="E106" s="23" t="str">
+      <c r="E107" s="23" t="str">
         <v>1. 修正液位后，立即更新液位和探头位置。
 2. 修复负数位置或读数变成异常大数的问题。
 3. 瓦锡兰测后回固定点最多尝试 3 次，失败后跳过探底并转回固定点
    监测。</v>
       </c>
-      <c r="F106" s="23" t="str">
+      <c r="F107" s="23" t="str">
         <v>原文仍列有部分水位计算及目标位置检查的待改进
 问题。</v>
       </c>
     </row>
-    <row r="107" ht="74" customHeight="1">
-      <c r="A107" s="26" t="n">
+    <row r="108" ht="74" customHeight="1">
+      <c r="A108" s="26" t="n">
         <v>46158</v>
       </c>
-      <c r="B107" s="28" t="str">
+      <c r="B108" s="28" t="str">
         <v>V1.7.1.2</v>
       </c>
-      <c r="C107" s="28" t="str">
+      <c r="C108" s="28" t="str">
         <v>V1.5.0.0</v>
       </c>
-      <c r="D107" s="24" t="str">
+      <c r="D108" s="24" t="str">
         <v>修复传感器切换及
 探头离底时的误报</v>
       </c>
-      <c r="E107" s="24" t="str">
+      <c r="E108" s="24" t="str">
         <v>1. 修复 LTD/V2 切换模式、读取部件参数时误报 13-13。
 2. 修正 DSM 传感器电压过低的提示。
 3. 改善瓦锡兰首个测点定位和退出固定点监测的处理。
 4. 减少探头离底时误报扭力故障的问题。</v>
       </c>
-      <c r="F107" s="24" t="str">
+      <c r="F108" s="24" t="str">
         <v>故障编号要按当时的程序版本查表。</v>
       </c>
     </row>
-    <row r="108" ht="48" customHeight="1">
-      <c r="A108" s="25" t="n">
+    <row r="109" ht="48" customHeight="1">
+      <c r="A109" s="25" t="n">
         <v>46157</v>
       </c>
-      <c r="B108" s="27" t="str">
+      <c r="B109" s="27" t="str">
         <v>V1.7.1.1</v>
       </c>
-      <c r="C108" s="27" t="str">
+      <c r="C109" s="27" t="str">
         <v>V1.5.0.0</v>
       </c>
-      <c r="D108" s="23" t="str">
+      <c r="D109" s="23" t="str">
         <v>故障后自动重测最多
 3 次</v>
       </c>
-      <c r="E108" s="23" t="str">
+      <c r="E109" s="23" t="str">
         <v>1. 同一次测量自动恢复后，最多重新测量 3 次。
 2. 达到上限后保持故障，避免一直重复测量。</v>
       </c>
-      <c r="F108" s="23" t="str">
+      <c r="F109" s="23" t="str">
         <v>部件检查仍会继续；后续版本可设置重试次数。</v>
       </c>
     </row>
-    <row r="109" ht="48" customHeight="1">
-      <c r="A109" s="26" t="n">
+    <row r="110" ht="48" customHeight="1">
+      <c r="A110" s="26" t="n">
         <v>46157</v>
       </c>
-      <c r="B109" s="28" t="str">
+      <c r="B110" s="28" t="str">
         <v>V1.7.1.0</v>
       </c>
-      <c r="C109" s="28" t="str">
+      <c r="C110" s="28" t="str">
         <v>V1.5.0.0</v>
       </c>
-      <c r="D109" s="24" t="str">
+      <c r="D110" s="24" t="str">
         <v>减少罐底误判和探头
 离底时的碰撞误报</v>
       </c>
-      <c r="E109" s="24" t="str">
+      <c r="E110" s="24" t="str">
         <v>1. 找罐底前先确认探头已离开罐底，避免一开始就误判找到。
 2. 减少探头离开罐底时误报扭力碰撞的问题。</v>
       </c>
-      <c r="F109" s="24" t="str">
+      <c r="F110" s="24" t="str">
         <v>涉及找罐底时探头离底上行的过程。</v>
       </c>
     </row>
-    <row r="110" ht="59" customHeight="1">
-      <c r="A110" s="25" t="n">
+    <row r="111" ht="59" customHeight="1">
+      <c r="A111" s="25" t="n">
         <v>46157</v>
       </c>
-      <c r="B110" s="27" t="str">
+      <c r="B111" s="27" t="str">
         <v>V1.7.0.0</v>
       </c>
-      <c r="C110" s="27" t="str">
+      <c r="C111" s="27" t="str">
         <v>V1.5.0.0</v>
       </c>
-      <c r="D110" s="23" t="str">
+      <c r="D111" s="23" t="str">
         <v>新增探底修正罐高与
 位置校正</v>
       </c>
-      <c r="E110" s="23" t="str">
+      <c r="E111" s="23" t="str">
         <v>1. 新增“探底修正罐高”，用于探底后校正探头位置。
 2. 测得的罐高偏差过大时，不进行位置校正。
 3. 调整瓦锡兰测量结束后回固定点及探底的先后过程。</v>
       </c>
-      <c r="F110" s="23" t="str">
+      <c r="F111" s="23" t="str">
         <v>新参数为 0 时仍使用液位罐高；两块板需配套升级。</v>
       </c>
     </row>
-    <row r="111" ht="59" customHeight="1">
-      <c r="A111" s="26" t="n">
+    <row r="112" ht="59" customHeight="1">
+      <c r="A112" s="26" t="n">
         <v>46157</v>
       </c>
-      <c r="B111" s="28" t="str">
+      <c r="B112" s="28" t="str">
         <v>V1.6.0.0</v>
       </c>
-      <c r="C111" s="28" t="str">
+      <c r="C112" s="28" t="str">
         <v>V1.4.0.0</v>
       </c>
-      <c r="D111" s="24" t="str">
+      <c r="D112" s="24" t="str">
         <v>新增长按返回停止
 测量和查看故障</v>
       </c>
-      <c r="E111" s="24" t="str">
+      <c r="E112" s="24" t="str">
         <v>1. 状态页长按返回键，再确认，可以停止测量并回到待机。
 2. 停止测量时，同时取消自动恢复。
 3. 故障时长按返回键，可以查看原因。</v>
       </c>
-      <c r="F111" s="24" t="str">
+      <c r="F112" s="24" t="str">
         <v>两块板需配套升级，旧主控程序不支持新增停止
 命令。</v>
       </c>
     </row>
-    <row r="112" ht="74" customHeight="1">
-      <c r="A112" s="25" t="n">
+    <row r="113" ht="74" customHeight="1">
+      <c r="A113" s="25" t="n">
         <v>46157</v>
       </c>
-      <c r="B112" s="27" t="str">
+      <c r="B113" s="27" t="str">
         <v>V1.5.1.0</v>
       </c>
-      <c r="C112" s="27" t="str">
+      <c r="C113" s="27" t="str">
         <v>V1.3.0.0</v>
       </c>
-      <c r="D112" s="23" t="str">
+      <c r="D113" s="23" t="str">
         <v>拦截错误传感器数据，
 修复回零误报</v>
       </c>
-      <c r="E112" s="23" t="str">
+      <c r="E113" s="23" t="str">
         <v>1. 收到不完整或错误的传感器数据时，不再当成正常读数。
 2. 新增 SC 通信测试，方便检查传感器连接。
 3. 修复 LTD/V2 传感器回零时，因不支持某些附加功能而误报故障的
    问题。</v>
       </c>
-      <c r="F112" s="23" t="str">
+      <c r="F113" s="23" t="str">
         <v>涉及 DSM、LTD/V2 和无线连接的传感器。</v>
       </c>
     </row>
-    <row r="113" ht="48" customHeight="1">
-      <c r="A113" s="26" t="n">
+    <row r="114" ht="48" customHeight="1">
+      <c r="A114" s="26" t="n">
         <v>46157</v>
       </c>
-      <c r="B113" s="28" t="str">
+      <c r="B114" s="28" t="str">
         <v>V1.5.0.0</v>
       </c>
-      <c r="C113" s="28" t="str">
+      <c r="C114" s="28" t="str">
         <v>V1.3.0.0</v>
       </c>
-      <c r="D113" s="24" t="str">
+      <c r="D114" s="24" t="str">
         <v>屏幕新增中文故障
 原因显示</v>
       </c>
-      <c r="E113" s="24" t="str">
+      <c r="E114" s="24" t="str">
         <v>1. 屏幕除了故障编号，还能显示中文原因。
 2. 较长的原因会分行显示，并补齐缺失文字。</v>
       </c>
-      <c r="F113" s="24" t="str">
+      <c r="F114" s="24" t="str">
         <v>后续版本调整了查看故障的操作入口。</v>
       </c>
     </row>
-    <row r="114" ht="59" customHeight="1">
-      <c r="A114" s="25" t="n">
+    <row r="115" ht="59" customHeight="1">
+      <c r="A115" s="25" t="n">
         <v>46156</v>
       </c>
-      <c r="B114" s="27" t="str">
+      <c r="B115" s="27" t="str">
         <v>V1.5.0.0</v>
       </c>
-      <c r="C114" s="27" t="str">
+      <c r="C115" s="27" t="str">
         <v>V1.2.0.0</v>
       </c>
-      <c r="D114" s="23" t="str">
+      <c r="D115" s="23" t="str">
         <v>分布测量由 100 点
 增加到 200 点</v>
       </c>
-      <c r="E114" s="23" t="str">
+      <c r="E115" s="23" t="str">
         <v>1. 分布测量最多可测 200 点，原来最多 100 点。
 2. 屏幕可设置 200 点，瓦锡兰系统也可读取新增测点。
 3. 状态页增加两块板通信不匹配的提示。</v>
       </c>
-      <c r="F114" s="23" t="str">
+      <c r="F115" s="23" t="str">
         <v>两块板需配套升级，原前 100 点的通信地址保留。</v>
       </c>
     </row>
-    <row r="115" ht="74" customHeight="1">
-      <c r="A115" s="26" t="n">
+    <row r="116" ht="74" customHeight="1">
+      <c r="A116" s="26" t="n">
         <v>46156</v>
       </c>
-      <c r="B115" s="28" t="str">
+      <c r="B116" s="28" t="str">
         <v>V1.4.1.0</v>
       </c>
-      <c r="C115" s="28" t="str">
+      <c r="C116" s="28" t="str">
         <v>V1.1.1.0</v>
       </c>
-      <c r="D115" s="24" t="str">
+      <c r="D116" s="24" t="str">
         <v>切换操作及时响应，
 修复误报与漏报</v>
       </c>
-      <c r="E115" s="24" t="str">
+      <c r="E116" s="24" t="str">
         <v>1. 等待读数稳定时，也能响应新的操作命令。
 2. 正常切换操作不再被误记为故障。
 3. 完善电机供电、传感器和滑环的故障区分。
 4. 修复固定点密度读取失败却没有报错的问题。</v>
       </c>
-      <c r="F115" s="24" t="str">
+      <c r="F116" s="24" t="str">
         <v>调整了两块板程序不匹配的提示规则。</v>
       </c>
     </row>
-    <row r="116" ht="48" customHeight="1">
-      <c r="A116" s="25" t="n">
+    <row r="117" ht="48" customHeight="1">
+      <c r="A117" s="25" t="n">
         <v>46155</v>
       </c>
-      <c r="B116" s="27" t="str">
+      <c r="B117" s="27" t="str">
         <v>V1.4.0.0</v>
       </c>
-      <c r="C116" s="27" t="str">
+      <c r="C117" s="27" t="str">
         <v>V1.1.0.0</v>
       </c>
-      <c r="D116" s="23" t="str">
+      <c r="D117" s="23" t="str">
         <v>日志区分重试过程与
 最终故障</v>
       </c>
-      <c r="E116" s="23" t="str">
+      <c r="E117" s="23" t="str">
         <v>1. 日志会分开显示正在重试、重试成功和最终故障。
 2. 修复实际故障原因被笼统的“失败”提示盖住的问题。</v>
       </c>
-      <c r="F116" s="23" t="str">
+      <c r="F117" s="23" t="str">
         <v>看到“重试”记录，不代表设备最终已报故障。</v>
       </c>
     </row>
-    <row r="117" ht="59" customHeight="1">
-      <c r="A117" s="26" t="n">
+    <row r="118" ht="59" customHeight="1">
+      <c r="A118" s="26" t="n">
         <v>46154</v>
       </c>
-      <c r="B117" s="28" t="str">
+      <c r="B118" s="28" t="str">
         <v>V1.3.0.0</v>
       </c>
-      <c r="C117" s="28" t="str">
+      <c r="C118" s="28" t="str">
         <v>V1.1.0.0</v>
       </c>
-      <c r="D117" s="24" t="str">
+      <c r="D118" s="24" t="str">
         <v>测量失败后自动检查
 并尝试恢复</v>
       </c>
-      <c r="E117" s="24" t="str">
+      <c r="E118" s="24" t="str">
         <v>1. 测量失败后自动检查各部件，恢复正常后再重新测量。
 2. 传感器通信失败后会重新尝试。
 3. 完善电机驱动复位后重新启动的处理。</v>
       </c>
-      <c r="F117" s="24" t="str">
+      <c r="F118" s="24" t="str">
         <v>恢复期间仍显示故障；后续版本增加了自动重试
 次数限制。</v>
       </c>
     </row>
-    <row r="118" ht="48" customHeight="1">
-      <c r="A118" s="25" t="n">
+    <row r="119" ht="48" customHeight="1">
+      <c r="A119" s="25" t="n">
         <v>46153</v>
       </c>
-      <c r="B118" s="27" t="str">
+      <c r="B119" s="27" t="str">
         <v>V1.2.1.0</v>
       </c>
-      <c r="C118" s="27" t="str">
+      <c r="C119" s="27" t="str">
         <v>V1.1.0.0</v>
       </c>
-      <c r="D118" s="23" t="str">
+      <c r="D119" s="23" t="str">
         <v>液位信号变化后重新
 找液面并跟随</v>
       </c>
-      <c r="E118" s="23" t="str">
+      <c r="E119" s="23" t="str">
         <v>1. 液位信号变化后，设备会重新找液面，找到后继续跟随。
 2. 连续读到异常频率时，会尝试切换测量模式恢复读数。</v>
       </c>
-      <c r="F118" s="23" t="str">
+      <c r="F119" s="23" t="str">
         <v>液位稳定时，保留已测得的液位值。</v>
       </c>
     </row>
-    <row r="119" ht="59" customHeight="1">
-      <c r="A119" s="26" t="n">
+    <row r="120" ht="59" customHeight="1">
+      <c r="A120" s="26" t="n">
         <v>46153</v>
       </c>
-      <c r="B119" s="28" t="str">
+      <c r="B120" s="28" t="str">
         <v>V1.2.0.0</v>
       </c>
-      <c r="C119" s="28" t="str">
+      <c r="C120" s="28" t="str">
         <v>V1.1.0.0</v>
       </c>
-      <c r="D119" s="24" t="str">
+      <c r="D120" s="24" t="str">
         <v>新增电机往返运行
 测试</v>
       </c>
-      <c r="E119" s="24" t="str">
+      <c r="E120" s="24" t="str">
         <v>1. 新增 BE 测试，可让电机在两个固定位置之间往返，方便检查运行
    距离。
 2. 修复新调试命令带入上一条命令内容的问题。</v>
       </c>
-      <c r="F119" s="24" t="str">
+      <c r="F120" s="24" t="str">
         <v>该测试通过主控板调试串口使用，屏幕没有新增
 按钮。</v>
       </c>
     </row>
-    <row r="120" ht="59" customHeight="1">
-      <c r="A120" s="25" t="n">
+    <row r="121" ht="59" customHeight="1">
+      <c r="A121" s="25" t="n">
         <v>46153</v>
       </c>
-      <c r="B120" s="27" t="str">
+      <c r="B121" s="27" t="str">
         <v>V1.1.0.0</v>
       </c>
-      <c r="C120" s="27" t="str">
+      <c r="C121" s="27" t="str">
         <v>V1.1.0.0</v>
       </c>
-      <c r="D120" s="23" t="str">
+      <c r="D121" s="23" t="str">
         <v>屏幕显示两板版本并
 提示不匹配</v>
       </c>
-      <c r="E120" s="23" t="str">
+      <c r="E121" s="23" t="str">
         <v>1. 屏幕可以查看主控板和显示板的程序版本。
 2. 两块板程序不匹配时，屏幕会提示。
 3. 修复升级后仍显示旧程序版本的问题。</v>
       </c>
-      <c r="F120" s="23" t="str">
+      <c r="F121" s="23" t="str">
         <v>早期版本和后续版本的配套判断方法不同，升级时
 以配套程序包为准。</v>
       </c>
     </row>
-    <row r="121" ht="48" customHeight="1">
-      <c r="A121" s="26" t="n">
+    <row r="122" ht="48" customHeight="1">
+      <c r="A122" s="26" t="n">
         <v>46153</v>
       </c>
-      <c r="B121" s="28" t="str">
+      <c r="B122" s="28" t="str">
         <v>V1.0.0.0</v>
       </c>
-      <c r="C121" s="28" t="str">
+      <c r="C122" s="28" t="str">
         <v>V1.0.0.0</v>
       </c>
-      <c r="D121" s="24" t="str">
+      <c r="D122" s="24" t="str">
         <v>主控板和显示板增加
 程序版本号</v>
       </c>
-      <c r="E121" s="24" t="str">
+      <c r="E122" s="24" t="str">
         <v>1. 主控板、显示板都有程序版本号，方便确认设备用的程序。</v>
       </c>
-      <c r="F121" s="24" t="str">
+      <c r="F122" s="24" t="str">
         <v>早期没有版本号的设备，升级前先记录现场参数。</v>
       </c>
     </row>
@@ -3316,23 +3356,29 @@
         <v>原文对应记录</v>
       </c>
     </row>
-    <row r="6" ht="59" customHeight="1">
-      <c r="A6" s="23" t="str">
-        <v>当前版本</v>
-      </c>
-      <c r="B6" s="23" t="str">
-        <v>CPU2 V1.43.0.0 / CPU3 V1.42.0.0</v>
+    <row r="6" ht="154" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当前版本</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPU2 V1.44.0.0 / CPU3 V1.43.0.0</t>
+        </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. 两块板需配套升级到协议 36。
-2. 液位定时矫正默认关闭，矫正周期默认 1 天。
-3. 需在设备允许修改参数时设置。</t>
+          <t xml:space="preserve">1. 两块板配套升级至协议 37。
+2. 原阈值数值保留，升级前记录并按减重量重新复核；固定下限 500 为原始计数。
+3. 称重探底阈值不能为 0。
+4. 需验证噪声、制动距离和 SI 首点配置；尚未完成目标板测试。
+5. 液位定时矫正仍默认关闭，默认周期 1 天。</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>2026-09-07 新增液位定时矫正</t>
+          <t xml:space="preserve">2026-09-07 称重探底与下行保护</t>
         </is>
       </c>
     </row>
